--- a/public/templates/phan-quyen-vmp.xlsx
+++ b/public/templates/phan-quyen-vmp.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>STT</t>
   </si>
@@ -29,10 +29,16 @@
     <t>Phân loại</t>
   </si>
   <si>
-    <t>Phạm vi</t>
+    <t>Phạm vi bộ phận</t>
   </si>
   <si>
-    <t>Khu vực phân quyền</t>
+    <t>Phạm vi xưởng</t>
+  </si>
+  <si>
+    <t>Phạm vi khu vực</t>
+  </si>
+  <si>
+    <t>Phạm vi line</t>
   </si>
   <si>
     <t>Email nhận tài khoản</t>
@@ -44,16 +50,16 @@
     <t>HƯỚNG DẪN NHẬP DANH BẠ NHÂN SỰ &amp; QUYỀN VMP</t>
   </si>
   <si>
-    <t>Mỗi người một dòng. Không đổi tên, thứ tự hoặc thêm bớt chín cột ở Trang tính1.</t>
+    <t>Mỗi người một dòng. Không đổi tên, thứ tự hoặc thêm bớt 11 cột ở Trang tính1.</t>
   </si>
   <si>
     <t>Mã nhân viên hiện không bắt buộc; có thể để trống và bổ sung sau. Hệ thống tạm khớp bằng Họ và tên có dấu, không phân biệt hoa thường và khoảng trắng.</t>
   </si>
   <si>
-    <t>Phạm vi: nhập mã bộ phận được xem/làm, nhiều giá trị cách nhau bằng dấu chấm phẩy; ví dụ QA;QC. Dùng * chỉ khi cần toàn bộ.</t>
+    <t>Bốn cột phạm vi nhập mã danh mục chuẩn, nhiều giá trị cách nhau bằng dấu chấm phẩy. Mỗi xưởng phải thuộc một bộ phận đã chọn, mỗi khu vực thuộc một xưởng đã chọn và mỗi line thuộc một khu vực đã chọn.</t>
   </si>
   <si>
-    <t>Khu vực phân quyền: nhập mã khu vực hoặc line, nhiều giá trị cách nhau bằng dấu chấm phẩy; ví dụ A1;A2. Dùng * chỉ khi cần toàn bộ.</t>
+    <t>Muốn cấp toàn bộ ở một tầng, nhập mã lựa chọn Toàn bộ đã được cấu hình trong danh mục; ô trống không có nghĩa là toàn bộ.</t>
   </si>
   <si>
     <t>Email nhận tài khoản: nếu trùng email của tài khoản hệ thống, danh bạ tự nối đúng user_id. Không dùng chung một email cho hai người.</t>
@@ -536,20 +542,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I501"/>
+  <dimension ref="A1:K501"/>
   <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
     <col min="5" max="5" width="52" customWidth="1"/>
-    <col min="6" max="6" width="24" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="32" customWidth="1"/>
-    <col min="9" max="9" width="24" customWidth="1"/>
+    <col min="6" max="9" width="24" customWidth="1"/>
+    <col min="10" max="10" width="32" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="34" customHeight="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -577,8 +582,14 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -590,8 +601,10 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -603,8 +616,10 @@
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -616,8 +631,10 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -629,8 +646,10 @@
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -642,8 +661,10 @@
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -655,8 +676,10 @@
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -668,8 +691,10 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -681,8 +706,10 @@
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -694,8 +721,10 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -707,8 +736,10 @@
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -720,8 +751,10 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -733,8 +766,10 @@
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -746,8 +781,10 @@
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -759,8 +796,10 @@
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -772,8 +811,10 @@
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -785,8 +826,10 @@
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -798,8 +841,10 @@
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -811,8 +856,10 @@
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -824,8 +871,10 @@
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -837,8 +886,10 @@
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -850,8 +901,10 @@
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -863,8 +916,10 @@
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -876,8 +931,10 @@
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -889,8 +946,10 @@
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -902,8 +961,10 @@
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -915,8 +976,10 @@
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -928,8 +991,10 @@
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -941,8 +1006,10 @@
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -954,8 +1021,10 @@
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -967,8 +1036,10 @@
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -980,8 +1051,10 @@
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -993,8 +1066,10 @@
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -1006,8 +1081,10 @@
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -1019,8 +1096,10 @@
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -1032,8 +1111,10 @@
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -1045,8 +1126,10 @@
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -1058,8 +1141,10 @@
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -1071,8 +1156,10 @@
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -1084,8 +1171,10 @@
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J40" s="3"/>
+      <c r="K40" s="3"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -1097,8 +1186,10 @@
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -1110,8 +1201,10 @@
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -1123,8 +1216,10 @@
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -1136,8 +1231,10 @@
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J44" s="3"/>
+      <c r="K44" s="3"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>44</v>
       </c>
@@ -1149,8 +1246,10 @@
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J45" s="4"/>
+      <c r="K45" s="4"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -1162,8 +1261,10 @@
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J46" s="3"/>
+      <c r="K46" s="3"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>46</v>
       </c>
@@ -1175,8 +1276,10 @@
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>47</v>
       </c>
@@ -1188,8 +1291,10 @@
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J48" s="3"/>
+      <c r="K48" s="3"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>48</v>
       </c>
@@ -1201,8 +1306,10 @@
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -1214,8 +1321,10 @@
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J50" s="3"/>
+      <c r="K50" s="3"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>50</v>
       </c>
@@ -1227,8 +1336,10 @@
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>51</v>
       </c>
@@ -1240,8 +1351,10 @@
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J52" s="3"/>
+      <c r="K52" s="3"/>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>52</v>
       </c>
@@ -1253,8 +1366,10 @@
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>53</v>
       </c>
@@ -1266,8 +1381,10 @@
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J54" s="3"/>
+      <c r="K54" s="3"/>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>54</v>
       </c>
@@ -1279,8 +1396,10 @@
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J55" s="4"/>
+      <c r="K55" s="4"/>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>55</v>
       </c>
@@ -1292,8 +1411,10 @@
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J56" s="3"/>
+      <c r="K56" s="3"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>56</v>
       </c>
@@ -1305,8 +1426,10 @@
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>57</v>
       </c>
@@ -1318,8 +1441,10 @@
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J58" s="3"/>
+      <c r="K58" s="3"/>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <v>58</v>
       </c>
@@ -1331,8 +1456,10 @@
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J59" s="4"/>
+      <c r="K59" s="4"/>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>59</v>
       </c>
@@ -1344,8 +1471,10 @@
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J60" s="3"/>
+      <c r="K60" s="3"/>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -1357,8 +1486,10 @@
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>61</v>
       </c>
@@ -1370,8 +1501,10 @@
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J62" s="3"/>
+      <c r="K62" s="3"/>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
         <v>62</v>
       </c>
@@ -1383,8 +1516,10 @@
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J63" s="4"/>
+      <c r="K63" s="4"/>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>63</v>
       </c>
@@ -1396,8 +1531,10 @@
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J64" s="3"/>
+      <c r="K64" s="3"/>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
         <v>64</v>
       </c>
@@ -1409,8 +1546,10 @@
       <c r="G65" s="4"/>
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J65" s="4"/>
+      <c r="K65" s="4"/>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>65</v>
       </c>
@@ -1422,8 +1561,10 @@
       <c r="G66" s="3"/>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J66" s="3"/>
+      <c r="K66" s="3"/>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
         <v>66</v>
       </c>
@@ -1435,8 +1576,10 @@
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J67" s="4"/>
+      <c r="K67" s="4"/>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>67</v>
       </c>
@@ -1448,8 +1591,10 @@
       <c r="G68" s="3"/>
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J68" s="3"/>
+      <c r="K68" s="3"/>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
         <v>68</v>
       </c>
@@ -1461,8 +1606,10 @@
       <c r="G69" s="4"/>
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J69" s="4"/>
+      <c r="K69" s="4"/>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>69</v>
       </c>
@@ -1474,8 +1621,10 @@
       <c r="G70" s="3"/>
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J70" s="3"/>
+      <c r="K70" s="3"/>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
         <v>70</v>
       </c>
@@ -1487,8 +1636,10 @@
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J71" s="4"/>
+      <c r="K71" s="4"/>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>71</v>
       </c>
@@ -1500,8 +1651,10 @@
       <c r="G72" s="3"/>
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J72" s="3"/>
+      <c r="K72" s="3"/>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
         <v>72</v>
       </c>
@@ -1513,8 +1666,10 @@
       <c r="G73" s="4"/>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J73" s="4"/>
+      <c r="K73" s="4"/>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
         <v>73</v>
       </c>
@@ -1526,8 +1681,10 @@
       <c r="G74" s="3"/>
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J74" s="3"/>
+      <c r="K74" s="3"/>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
         <v>74</v>
       </c>
@@ -1539,8 +1696,10 @@
       <c r="G75" s="4"/>
       <c r="H75" s="4"/>
       <c r="I75" s="4"/>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J75" s="4"/>
+      <c r="K75" s="4"/>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>75</v>
       </c>
@@ -1552,8 +1711,10 @@
       <c r="G76" s="3"/>
       <c r="H76" s="3"/>
       <c r="I76" s="3"/>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J76" s="3"/>
+      <c r="K76" s="3"/>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
         <v>76</v>
       </c>
@@ -1565,8 +1726,10 @@
       <c r="G77" s="4"/>
       <c r="H77" s="4"/>
       <c r="I77" s="4"/>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J77" s="4"/>
+      <c r="K77" s="4"/>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>77</v>
       </c>
@@ -1578,8 +1741,10 @@
       <c r="G78" s="3"/>
       <c r="H78" s="3"/>
       <c r="I78" s="3"/>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J78" s="3"/>
+      <c r="K78" s="3"/>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
         <v>78</v>
       </c>
@@ -1591,8 +1756,10 @@
       <c r="G79" s="4"/>
       <c r="H79" s="4"/>
       <c r="I79" s="4"/>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J79" s="4"/>
+      <c r="K79" s="4"/>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>79</v>
       </c>
@@ -1604,8 +1771,10 @@
       <c r="G80" s="3"/>
       <c r="H80" s="3"/>
       <c r="I80" s="3"/>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J80" s="3"/>
+      <c r="K80" s="3"/>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
         <v>80</v>
       </c>
@@ -1617,8 +1786,10 @@
       <c r="G81" s="4"/>
       <c r="H81" s="4"/>
       <c r="I81" s="4"/>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J81" s="4"/>
+      <c r="K81" s="4"/>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
         <v>81</v>
       </c>
@@ -1630,8 +1801,10 @@
       <c r="G82" s="3"/>
       <c r="H82" s="3"/>
       <c r="I82" s="3"/>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J82" s="3"/>
+      <c r="K82" s="3"/>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
         <v>82</v>
       </c>
@@ -1643,8 +1816,10 @@
       <c r="G83" s="4"/>
       <c r="H83" s="4"/>
       <c r="I83" s="4"/>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J83" s="4"/>
+      <c r="K83" s="4"/>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
         <v>83</v>
       </c>
@@ -1656,8 +1831,10 @@
       <c r="G84" s="3"/>
       <c r="H84" s="3"/>
       <c r="I84" s="3"/>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J84" s="3"/>
+      <c r="K84" s="3"/>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
         <v>84</v>
       </c>
@@ -1669,8 +1846,10 @@
       <c r="G85" s="4"/>
       <c r="H85" s="4"/>
       <c r="I85" s="4"/>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J85" s="4"/>
+      <c r="K85" s="4"/>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
         <v>85</v>
       </c>
@@ -1682,8 +1861,10 @@
       <c r="G86" s="3"/>
       <c r="H86" s="3"/>
       <c r="I86" s="3"/>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J86" s="3"/>
+      <c r="K86" s="3"/>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="4">
         <v>86</v>
       </c>
@@ -1695,8 +1876,10 @@
       <c r="G87" s="4"/>
       <c r="H87" s="4"/>
       <c r="I87" s="4"/>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J87" s="4"/>
+      <c r="K87" s="4"/>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>87</v>
       </c>
@@ -1708,8 +1891,10 @@
       <c r="G88" s="3"/>
       <c r="H88" s="3"/>
       <c r="I88" s="3"/>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J88" s="3"/>
+      <c r="K88" s="3"/>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="4">
         <v>88</v>
       </c>
@@ -1721,8 +1906,10 @@
       <c r="G89" s="4"/>
       <c r="H89" s="4"/>
       <c r="I89" s="4"/>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J89" s="4"/>
+      <c r="K89" s="4"/>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>89</v>
       </c>
@@ -1734,8 +1921,10 @@
       <c r="G90" s="3"/>
       <c r="H90" s="3"/>
       <c r="I90" s="3"/>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J90" s="3"/>
+      <c r="K90" s="3"/>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="4">
         <v>90</v>
       </c>
@@ -1747,8 +1936,10 @@
       <c r="G91" s="4"/>
       <c r="H91" s="4"/>
       <c r="I91" s="4"/>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J91" s="4"/>
+      <c r="K91" s="4"/>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>91</v>
       </c>
@@ -1760,8 +1951,10 @@
       <c r="G92" s="3"/>
       <c r="H92" s="3"/>
       <c r="I92" s="3"/>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J92" s="3"/>
+      <c r="K92" s="3"/>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="4">
         <v>92</v>
       </c>
@@ -1773,8 +1966,10 @@
       <c r="G93" s="4"/>
       <c r="H93" s="4"/>
       <c r="I93" s="4"/>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J93" s="4"/>
+      <c r="K93" s="4"/>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
         <v>93</v>
       </c>
@@ -1786,8 +1981,10 @@
       <c r="G94" s="3"/>
       <c r="H94" s="3"/>
       <c r="I94" s="3"/>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J94" s="3"/>
+      <c r="K94" s="3"/>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="4">
         <v>94</v>
       </c>
@@ -1799,8 +1996,10 @@
       <c r="G95" s="4"/>
       <c r="H95" s="4"/>
       <c r="I95" s="4"/>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J95" s="4"/>
+      <c r="K95" s="4"/>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
         <v>95</v>
       </c>
@@ -1812,8 +2011,10 @@
       <c r="G96" s="3"/>
       <c r="H96" s="3"/>
       <c r="I96" s="3"/>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J96" s="3"/>
+      <c r="K96" s="3"/>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="4">
         <v>96</v>
       </c>
@@ -1825,8 +2026,10 @@
       <c r="G97" s="4"/>
       <c r="H97" s="4"/>
       <c r="I97" s="4"/>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J97" s="4"/>
+      <c r="K97" s="4"/>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
         <v>97</v>
       </c>
@@ -1838,8 +2041,10 @@
       <c r="G98" s="3"/>
       <c r="H98" s="3"/>
       <c r="I98" s="3"/>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J98" s="3"/>
+      <c r="K98" s="3"/>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="4">
         <v>98</v>
       </c>
@@ -1851,8 +2056,10 @@
       <c r="G99" s="4"/>
       <c r="H99" s="4"/>
       <c r="I99" s="4"/>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J99" s="4"/>
+      <c r="K99" s="4"/>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
         <v>99</v>
       </c>
@@ -1864,8 +2071,10 @@
       <c r="G100" s="3"/>
       <c r="H100" s="3"/>
       <c r="I100" s="3"/>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J100" s="3"/>
+      <c r="K100" s="3"/>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="4">
         <v>100</v>
       </c>
@@ -1877,8 +2086,10 @@
       <c r="G101" s="4"/>
       <c r="H101" s="4"/>
       <c r="I101" s="4"/>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J101" s="4"/>
+      <c r="K101" s="4"/>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
         <v>101</v>
       </c>
@@ -1890,8 +2101,10 @@
       <c r="G102" s="3"/>
       <c r="H102" s="3"/>
       <c r="I102" s="3"/>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J102" s="3"/>
+      <c r="K102" s="3"/>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="4">
         <v>102</v>
       </c>
@@ -1903,8 +2116,10 @@
       <c r="G103" s="4"/>
       <c r="H103" s="4"/>
       <c r="I103" s="4"/>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J103" s="4"/>
+      <c r="K103" s="4"/>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
         <v>103</v>
       </c>
@@ -1916,8 +2131,10 @@
       <c r="G104" s="3"/>
       <c r="H104" s="3"/>
       <c r="I104" s="3"/>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J104" s="3"/>
+      <c r="K104" s="3"/>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="4">
         <v>104</v>
       </c>
@@ -1929,8 +2146,10 @@
       <c r="G105" s="4"/>
       <c r="H105" s="4"/>
       <c r="I105" s="4"/>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J105" s="4"/>
+      <c r="K105" s="4"/>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
         <v>105</v>
       </c>
@@ -1942,8 +2161,10 @@
       <c r="G106" s="3"/>
       <c r="H106" s="3"/>
       <c r="I106" s="3"/>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J106" s="3"/>
+      <c r="K106" s="3"/>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="4">
         <v>106</v>
       </c>
@@ -1955,8 +2176,10 @@
       <c r="G107" s="4"/>
       <c r="H107" s="4"/>
       <c r="I107" s="4"/>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J107" s="4"/>
+      <c r="K107" s="4"/>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
         <v>107</v>
       </c>
@@ -1968,8 +2191,10 @@
       <c r="G108" s="3"/>
       <c r="H108" s="3"/>
       <c r="I108" s="3"/>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J108" s="3"/>
+      <c r="K108" s="3"/>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="4">
         <v>108</v>
       </c>
@@ -1981,8 +2206,10 @@
       <c r="G109" s="4"/>
       <c r="H109" s="4"/>
       <c r="I109" s="4"/>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J109" s="4"/>
+      <c r="K109" s="4"/>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
         <v>109</v>
       </c>
@@ -1994,8 +2221,10 @@
       <c r="G110" s="3"/>
       <c r="H110" s="3"/>
       <c r="I110" s="3"/>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J110" s="3"/>
+      <c r="K110" s="3"/>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="4">
         <v>110</v>
       </c>
@@ -2007,8 +2236,10 @@
       <c r="G111" s="4"/>
       <c r="H111" s="4"/>
       <c r="I111" s="4"/>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J111" s="4"/>
+      <c r="K111" s="4"/>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
         <v>111</v>
       </c>
@@ -2020,8 +2251,10 @@
       <c r="G112" s="3"/>
       <c r="H112" s="3"/>
       <c r="I112" s="3"/>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J112" s="3"/>
+      <c r="K112" s="3"/>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" s="4">
         <v>112</v>
       </c>
@@ -2033,8 +2266,10 @@
       <c r="G113" s="4"/>
       <c r="H113" s="4"/>
       <c r="I113" s="4"/>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J113" s="4"/>
+      <c r="K113" s="4"/>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" s="3">
         <v>113</v>
       </c>
@@ -2046,8 +2281,10 @@
       <c r="G114" s="3"/>
       <c r="H114" s="3"/>
       <c r="I114" s="3"/>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J114" s="3"/>
+      <c r="K114" s="3"/>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" s="4">
         <v>114</v>
       </c>
@@ -2059,8 +2296,10 @@
       <c r="G115" s="4"/>
       <c r="H115" s="4"/>
       <c r="I115" s="4"/>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J115" s="4"/>
+      <c r="K115" s="4"/>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="3">
         <v>115</v>
       </c>
@@ -2072,8 +2311,10 @@
       <c r="G116" s="3"/>
       <c r="H116" s="3"/>
       <c r="I116" s="3"/>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J116" s="3"/>
+      <c r="K116" s="3"/>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" s="4">
         <v>116</v>
       </c>
@@ -2085,8 +2326,10 @@
       <c r="G117" s="4"/>
       <c r="H117" s="4"/>
       <c r="I117" s="4"/>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J117" s="4"/>
+      <c r="K117" s="4"/>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" s="3">
         <v>117</v>
       </c>
@@ -2098,8 +2341,10 @@
       <c r="G118" s="3"/>
       <c r="H118" s="3"/>
       <c r="I118" s="3"/>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J118" s="3"/>
+      <c r="K118" s="3"/>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" s="4">
         <v>118</v>
       </c>
@@ -2111,8 +2356,10 @@
       <c r="G119" s="4"/>
       <c r="H119" s="4"/>
       <c r="I119" s="4"/>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J119" s="4"/>
+      <c r="K119" s="4"/>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" s="3">
         <v>119</v>
       </c>
@@ -2124,8 +2371,10 @@
       <c r="G120" s="3"/>
       <c r="H120" s="3"/>
       <c r="I120" s="3"/>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J120" s="3"/>
+      <c r="K120" s="3"/>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" s="4">
         <v>120</v>
       </c>
@@ -2137,8 +2386,10 @@
       <c r="G121" s="4"/>
       <c r="H121" s="4"/>
       <c r="I121" s="4"/>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J121" s="4"/>
+      <c r="K121" s="4"/>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" s="3">
         <v>121</v>
       </c>
@@ -2150,8 +2401,10 @@
       <c r="G122" s="3"/>
       <c r="H122" s="3"/>
       <c r="I122" s="3"/>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J122" s="3"/>
+      <c r="K122" s="3"/>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" s="4">
         <v>122</v>
       </c>
@@ -2163,8 +2416,10 @@
       <c r="G123" s="4"/>
       <c r="H123" s="4"/>
       <c r="I123" s="4"/>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J123" s="4"/>
+      <c r="K123" s="4"/>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" s="3">
         <v>123</v>
       </c>
@@ -2176,8 +2431,10 @@
       <c r="G124" s="3"/>
       <c r="H124" s="3"/>
       <c r="I124" s="3"/>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J124" s="3"/>
+      <c r="K124" s="3"/>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" s="4">
         <v>124</v>
       </c>
@@ -2189,8 +2446,10 @@
       <c r="G125" s="4"/>
       <c r="H125" s="4"/>
       <c r="I125" s="4"/>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J125" s="4"/>
+      <c r="K125" s="4"/>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="3">
         <v>125</v>
       </c>
@@ -2202,8 +2461,10 @@
       <c r="G126" s="3"/>
       <c r="H126" s="3"/>
       <c r="I126" s="3"/>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J126" s="3"/>
+      <c r="K126" s="3"/>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" s="4">
         <v>126</v>
       </c>
@@ -2215,8 +2476,10 @@
       <c r="G127" s="4"/>
       <c r="H127" s="4"/>
       <c r="I127" s="4"/>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J127" s="4"/>
+      <c r="K127" s="4"/>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" s="3">
         <v>127</v>
       </c>
@@ -2228,8 +2491,10 @@
       <c r="G128" s="3"/>
       <c r="H128" s="3"/>
       <c r="I128" s="3"/>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J128" s="3"/>
+      <c r="K128" s="3"/>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" s="4">
         <v>128</v>
       </c>
@@ -2241,8 +2506,10 @@
       <c r="G129" s="4"/>
       <c r="H129" s="4"/>
       <c r="I129" s="4"/>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J129" s="4"/>
+      <c r="K129" s="4"/>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" s="3">
         <v>129</v>
       </c>
@@ -2254,8 +2521,10 @@
       <c r="G130" s="3"/>
       <c r="H130" s="3"/>
       <c r="I130" s="3"/>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J130" s="3"/>
+      <c r="K130" s="3"/>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" s="4">
         <v>130</v>
       </c>
@@ -2267,8 +2536,10 @@
       <c r="G131" s="4"/>
       <c r="H131" s="4"/>
       <c r="I131" s="4"/>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J131" s="4"/>
+      <c r="K131" s="4"/>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" s="3">
         <v>131</v>
       </c>
@@ -2280,8 +2551,10 @@
       <c r="G132" s="3"/>
       <c r="H132" s="3"/>
       <c r="I132" s="3"/>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J132" s="3"/>
+      <c r="K132" s="3"/>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" s="4">
         <v>132</v>
       </c>
@@ -2293,8 +2566,10 @@
       <c r="G133" s="4"/>
       <c r="H133" s="4"/>
       <c r="I133" s="4"/>
-    </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J133" s="4"/>
+      <c r="K133" s="4"/>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" s="3">
         <v>133</v>
       </c>
@@ -2306,8 +2581,10 @@
       <c r="G134" s="3"/>
       <c r="H134" s="3"/>
       <c r="I134" s="3"/>
-    </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J134" s="3"/>
+      <c r="K134" s="3"/>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" s="4">
         <v>134</v>
       </c>
@@ -2319,8 +2596,10 @@
       <c r="G135" s="4"/>
       <c r="H135" s="4"/>
       <c r="I135" s="4"/>
-    </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J135" s="4"/>
+      <c r="K135" s="4"/>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" s="3">
         <v>135</v>
       </c>
@@ -2332,8 +2611,10 @@
       <c r="G136" s="3"/>
       <c r="H136" s="3"/>
       <c r="I136" s="3"/>
-    </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J136" s="3"/>
+      <c r="K136" s="3"/>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" s="4">
         <v>136</v>
       </c>
@@ -2345,8 +2626,10 @@
       <c r="G137" s="4"/>
       <c r="H137" s="4"/>
       <c r="I137" s="4"/>
-    </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J137" s="4"/>
+      <c r="K137" s="4"/>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" s="3">
         <v>137</v>
       </c>
@@ -2358,8 +2641,10 @@
       <c r="G138" s="3"/>
       <c r="H138" s="3"/>
       <c r="I138" s="3"/>
-    </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J138" s="3"/>
+      <c r="K138" s="3"/>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" s="4">
         <v>138</v>
       </c>
@@ -2371,8 +2656,10 @@
       <c r="G139" s="4"/>
       <c r="H139" s="4"/>
       <c r="I139" s="4"/>
-    </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J139" s="4"/>
+      <c r="K139" s="4"/>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" s="3">
         <v>139</v>
       </c>
@@ -2384,8 +2671,10 @@
       <c r="G140" s="3"/>
       <c r="H140" s="3"/>
       <c r="I140" s="3"/>
-    </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J140" s="3"/>
+      <c r="K140" s="3"/>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" s="4">
         <v>140</v>
       </c>
@@ -2397,8 +2686,10 @@
       <c r="G141" s="4"/>
       <c r="H141" s="4"/>
       <c r="I141" s="4"/>
-    </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J141" s="4"/>
+      <c r="K141" s="4"/>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" s="3">
         <v>141</v>
       </c>
@@ -2410,8 +2701,10 @@
       <c r="G142" s="3"/>
       <c r="H142" s="3"/>
       <c r="I142" s="3"/>
-    </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J142" s="3"/>
+      <c r="K142" s="3"/>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" s="4">
         <v>142</v>
       </c>
@@ -2423,8 +2716,10 @@
       <c r="G143" s="4"/>
       <c r="H143" s="4"/>
       <c r="I143" s="4"/>
-    </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J143" s="4"/>
+      <c r="K143" s="4"/>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" s="3">
         <v>143</v>
       </c>
@@ -2436,8 +2731,10 @@
       <c r="G144" s="3"/>
       <c r="H144" s="3"/>
       <c r="I144" s="3"/>
-    </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J144" s="3"/>
+      <c r="K144" s="3"/>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" s="4">
         <v>144</v>
       </c>
@@ -2449,8 +2746,10 @@
       <c r="G145" s="4"/>
       <c r="H145" s="4"/>
       <c r="I145" s="4"/>
-    </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J145" s="4"/>
+      <c r="K145" s="4"/>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" s="3">
         <v>145</v>
       </c>
@@ -2462,8 +2761,10 @@
       <c r="G146" s="3"/>
       <c r="H146" s="3"/>
       <c r="I146" s="3"/>
-    </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J146" s="3"/>
+      <c r="K146" s="3"/>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" s="4">
         <v>146</v>
       </c>
@@ -2475,8 +2776,10 @@
       <c r="G147" s="4"/>
       <c r="H147" s="4"/>
       <c r="I147" s="4"/>
-    </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J147" s="4"/>
+      <c r="K147" s="4"/>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" s="3">
         <v>147</v>
       </c>
@@ -2488,8 +2791,10 @@
       <c r="G148" s="3"/>
       <c r="H148" s="3"/>
       <c r="I148" s="3"/>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J148" s="3"/>
+      <c r="K148" s="3"/>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" s="4">
         <v>148</v>
       </c>
@@ -2501,8 +2806,10 @@
       <c r="G149" s="4"/>
       <c r="H149" s="4"/>
       <c r="I149" s="4"/>
-    </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J149" s="4"/>
+      <c r="K149" s="4"/>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" s="3">
         <v>149</v>
       </c>
@@ -2514,8 +2821,10 @@
       <c r="G150" s="3"/>
       <c r="H150" s="3"/>
       <c r="I150" s="3"/>
-    </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J150" s="3"/>
+      <c r="K150" s="3"/>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" s="4">
         <v>150</v>
       </c>
@@ -2527,8 +2836,10 @@
       <c r="G151" s="4"/>
       <c r="H151" s="4"/>
       <c r="I151" s="4"/>
-    </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J151" s="4"/>
+      <c r="K151" s="4"/>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" s="3">
         <v>151</v>
       </c>
@@ -2540,8 +2851,10 @@
       <c r="G152" s="3"/>
       <c r="H152" s="3"/>
       <c r="I152" s="3"/>
-    </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J152" s="3"/>
+      <c r="K152" s="3"/>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" s="4">
         <v>152</v>
       </c>
@@ -2553,8 +2866,10 @@
       <c r="G153" s="4"/>
       <c r="H153" s="4"/>
       <c r="I153" s="4"/>
-    </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J153" s="4"/>
+      <c r="K153" s="4"/>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" s="3">
         <v>153</v>
       </c>
@@ -2566,8 +2881,10 @@
       <c r="G154" s="3"/>
       <c r="H154" s="3"/>
       <c r="I154" s="3"/>
-    </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J154" s="3"/>
+      <c r="K154" s="3"/>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" s="4">
         <v>154</v>
       </c>
@@ -2579,8 +2896,10 @@
       <c r="G155" s="4"/>
       <c r="H155" s="4"/>
       <c r="I155" s="4"/>
-    </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J155" s="4"/>
+      <c r="K155" s="4"/>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" s="3">
         <v>155</v>
       </c>
@@ -2592,8 +2911,10 @@
       <c r="G156" s="3"/>
       <c r="H156" s="3"/>
       <c r="I156" s="3"/>
-    </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J156" s="3"/>
+      <c r="K156" s="3"/>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157" s="4">
         <v>156</v>
       </c>
@@ -2605,8 +2926,10 @@
       <c r="G157" s="4"/>
       <c r="H157" s="4"/>
       <c r="I157" s="4"/>
-    </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J157" s="4"/>
+      <c r="K157" s="4"/>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" s="3">
         <v>157</v>
       </c>
@@ -2618,8 +2941,10 @@
       <c r="G158" s="3"/>
       <c r="H158" s="3"/>
       <c r="I158" s="3"/>
-    </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J158" s="3"/>
+      <c r="K158" s="3"/>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" s="4">
         <v>158</v>
       </c>
@@ -2631,8 +2956,10 @@
       <c r="G159" s="4"/>
       <c r="H159" s="4"/>
       <c r="I159" s="4"/>
-    </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J159" s="4"/>
+      <c r="K159" s="4"/>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" s="3">
         <v>159</v>
       </c>
@@ -2644,8 +2971,10 @@
       <c r="G160" s="3"/>
       <c r="H160" s="3"/>
       <c r="I160" s="3"/>
-    </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J160" s="3"/>
+      <c r="K160" s="3"/>
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" s="4">
         <v>160</v>
       </c>
@@ -2657,8 +2986,10 @@
       <c r="G161" s="4"/>
       <c r="H161" s="4"/>
       <c r="I161" s="4"/>
-    </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J161" s="4"/>
+      <c r="K161" s="4"/>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" s="3">
         <v>161</v>
       </c>
@@ -2670,8 +3001,10 @@
       <c r="G162" s="3"/>
       <c r="H162" s="3"/>
       <c r="I162" s="3"/>
-    </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J162" s="3"/>
+      <c r="K162" s="3"/>
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" s="4">
         <v>162</v>
       </c>
@@ -2683,8 +3016,10 @@
       <c r="G163" s="4"/>
       <c r="H163" s="4"/>
       <c r="I163" s="4"/>
-    </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J163" s="4"/>
+      <c r="K163" s="4"/>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" s="3">
         <v>163</v>
       </c>
@@ -2696,8 +3031,10 @@
       <c r="G164" s="3"/>
       <c r="H164" s="3"/>
       <c r="I164" s="3"/>
-    </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J164" s="3"/>
+      <c r="K164" s="3"/>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165" s="4">
         <v>164</v>
       </c>
@@ -2709,8 +3046,10 @@
       <c r="G165" s="4"/>
       <c r="H165" s="4"/>
       <c r="I165" s="4"/>
-    </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J165" s="4"/>
+      <c r="K165" s="4"/>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" s="3">
         <v>165</v>
       </c>
@@ -2722,8 +3061,10 @@
       <c r="G166" s="3"/>
       <c r="H166" s="3"/>
       <c r="I166" s="3"/>
-    </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J166" s="3"/>
+      <c r="K166" s="3"/>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" s="4">
         <v>166</v>
       </c>
@@ -2735,8 +3076,10 @@
       <c r="G167" s="4"/>
       <c r="H167" s="4"/>
       <c r="I167" s="4"/>
-    </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J167" s="4"/>
+      <c r="K167" s="4"/>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" s="3">
         <v>167</v>
       </c>
@@ -2748,8 +3091,10 @@
       <c r="G168" s="3"/>
       <c r="H168" s="3"/>
       <c r="I168" s="3"/>
-    </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J168" s="3"/>
+      <c r="K168" s="3"/>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" s="4">
         <v>168</v>
       </c>
@@ -2761,8 +3106,10 @@
       <c r="G169" s="4"/>
       <c r="H169" s="4"/>
       <c r="I169" s="4"/>
-    </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J169" s="4"/>
+      <c r="K169" s="4"/>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" s="3">
         <v>169</v>
       </c>
@@ -2774,8 +3121,10 @@
       <c r="G170" s="3"/>
       <c r="H170" s="3"/>
       <c r="I170" s="3"/>
-    </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J170" s="3"/>
+      <c r="K170" s="3"/>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" s="4">
         <v>170</v>
       </c>
@@ -2787,8 +3136,10 @@
       <c r="G171" s="4"/>
       <c r="H171" s="4"/>
       <c r="I171" s="4"/>
-    </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J171" s="4"/>
+      <c r="K171" s="4"/>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" s="3">
         <v>171</v>
       </c>
@@ -2800,8 +3151,10 @@
       <c r="G172" s="3"/>
       <c r="H172" s="3"/>
       <c r="I172" s="3"/>
-    </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J172" s="3"/>
+      <c r="K172" s="3"/>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" s="4">
         <v>172</v>
       </c>
@@ -2813,8 +3166,10 @@
       <c r="G173" s="4"/>
       <c r="H173" s="4"/>
       <c r="I173" s="4"/>
-    </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J173" s="4"/>
+      <c r="K173" s="4"/>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" s="3">
         <v>173</v>
       </c>
@@ -2826,8 +3181,10 @@
       <c r="G174" s="3"/>
       <c r="H174" s="3"/>
       <c r="I174" s="3"/>
-    </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J174" s="3"/>
+      <c r="K174" s="3"/>
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175" s="4">
         <v>174</v>
       </c>
@@ -2839,8 +3196,10 @@
       <c r="G175" s="4"/>
       <c r="H175" s="4"/>
       <c r="I175" s="4"/>
-    </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J175" s="4"/>
+      <c r="K175" s="4"/>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176" s="3">
         <v>175</v>
       </c>
@@ -2852,8 +3211,10 @@
       <c r="G176" s="3"/>
       <c r="H176" s="3"/>
       <c r="I176" s="3"/>
-    </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J176" s="3"/>
+      <c r="K176" s="3"/>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177" s="4">
         <v>176</v>
       </c>
@@ -2865,8 +3226,10 @@
       <c r="G177" s="4"/>
       <c r="H177" s="4"/>
       <c r="I177" s="4"/>
-    </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J177" s="4"/>
+      <c r="K177" s="4"/>
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178" s="3">
         <v>177</v>
       </c>
@@ -2878,8 +3241,10 @@
       <c r="G178" s="3"/>
       <c r="H178" s="3"/>
       <c r="I178" s="3"/>
-    </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J178" s="3"/>
+      <c r="K178" s="3"/>
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179" s="4">
         <v>178</v>
       </c>
@@ -2891,8 +3256,10 @@
       <c r="G179" s="4"/>
       <c r="H179" s="4"/>
       <c r="I179" s="4"/>
-    </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J179" s="4"/>
+      <c r="K179" s="4"/>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180" s="3">
         <v>179</v>
       </c>
@@ -2904,8 +3271,10 @@
       <c r="G180" s="3"/>
       <c r="H180" s="3"/>
       <c r="I180" s="3"/>
-    </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J180" s="3"/>
+      <c r="K180" s="3"/>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181" s="4">
         <v>180</v>
       </c>
@@ -2917,8 +3286,10 @@
       <c r="G181" s="4"/>
       <c r="H181" s="4"/>
       <c r="I181" s="4"/>
-    </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J181" s="4"/>
+      <c r="K181" s="4"/>
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182" s="3">
         <v>181</v>
       </c>
@@ -2930,8 +3301,10 @@
       <c r="G182" s="3"/>
       <c r="H182" s="3"/>
       <c r="I182" s="3"/>
-    </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J182" s="3"/>
+      <c r="K182" s="3"/>
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183" s="4">
         <v>182</v>
       </c>
@@ -2943,8 +3316,10 @@
       <c r="G183" s="4"/>
       <c r="H183" s="4"/>
       <c r="I183" s="4"/>
-    </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J183" s="4"/>
+      <c r="K183" s="4"/>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184" s="3">
         <v>183</v>
       </c>
@@ -2956,8 +3331,10 @@
       <c r="G184" s="3"/>
       <c r="H184" s="3"/>
       <c r="I184" s="3"/>
-    </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J184" s="3"/>
+      <c r="K184" s="3"/>
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185" s="4">
         <v>184</v>
       </c>
@@ -2969,8 +3346,10 @@
       <c r="G185" s="4"/>
       <c r="H185" s="4"/>
       <c r="I185" s="4"/>
-    </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J185" s="4"/>
+      <c r="K185" s="4"/>
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186" s="3">
         <v>185</v>
       </c>
@@ -2982,8 +3361,10 @@
       <c r="G186" s="3"/>
       <c r="H186" s="3"/>
       <c r="I186" s="3"/>
-    </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J186" s="3"/>
+      <c r="K186" s="3"/>
+    </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187" s="4">
         <v>186</v>
       </c>
@@ -2995,8 +3376,10 @@
       <c r="G187" s="4"/>
       <c r="H187" s="4"/>
       <c r="I187" s="4"/>
-    </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J187" s="4"/>
+      <c r="K187" s="4"/>
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188" s="3">
         <v>187</v>
       </c>
@@ -3008,8 +3391,10 @@
       <c r="G188" s="3"/>
       <c r="H188" s="3"/>
       <c r="I188" s="3"/>
-    </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J188" s="3"/>
+      <c r="K188" s="3"/>
+    </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189" s="4">
         <v>188</v>
       </c>
@@ -3021,8 +3406,10 @@
       <c r="G189" s="4"/>
       <c r="H189" s="4"/>
       <c r="I189" s="4"/>
-    </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J189" s="4"/>
+      <c r="K189" s="4"/>
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190" s="3">
         <v>189</v>
       </c>
@@ -3034,8 +3421,10 @@
       <c r="G190" s="3"/>
       <c r="H190" s="3"/>
       <c r="I190" s="3"/>
-    </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J190" s="3"/>
+      <c r="K190" s="3"/>
+    </row>
+    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191" s="4">
         <v>190</v>
       </c>
@@ -3047,8 +3436,10 @@
       <c r="G191" s="4"/>
       <c r="H191" s="4"/>
       <c r="I191" s="4"/>
-    </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J191" s="4"/>
+      <c r="K191" s="4"/>
+    </row>
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192" s="3">
         <v>191</v>
       </c>
@@ -3060,8 +3451,10 @@
       <c r="G192" s="3"/>
       <c r="H192" s="3"/>
       <c r="I192" s="3"/>
-    </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J192" s="3"/>
+      <c r="K192" s="3"/>
+    </row>
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A193" s="4">
         <v>192</v>
       </c>
@@ -3073,8 +3466,10 @@
       <c r="G193" s="4"/>
       <c r="H193" s="4"/>
       <c r="I193" s="4"/>
-    </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J193" s="4"/>
+      <c r="K193" s="4"/>
+    </row>
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194" s="3">
         <v>193</v>
       </c>
@@ -3086,8 +3481,10 @@
       <c r="G194" s="3"/>
       <c r="H194" s="3"/>
       <c r="I194" s="3"/>
-    </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J194" s="3"/>
+      <c r="K194" s="3"/>
+    </row>
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195" s="4">
         <v>194</v>
       </c>
@@ -3099,8 +3496,10 @@
       <c r="G195" s="4"/>
       <c r="H195" s="4"/>
       <c r="I195" s="4"/>
-    </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J195" s="4"/>
+      <c r="K195" s="4"/>
+    </row>
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A196" s="3">
         <v>195</v>
       </c>
@@ -3112,8 +3511,10 @@
       <c r="G196" s="3"/>
       <c r="H196" s="3"/>
       <c r="I196" s="3"/>
-    </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J196" s="3"/>
+      <c r="K196" s="3"/>
+    </row>
+    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A197" s="4">
         <v>196</v>
       </c>
@@ -3125,8 +3526,10 @@
       <c r="G197" s="4"/>
       <c r="H197" s="4"/>
       <c r="I197" s="4"/>
-    </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J197" s="4"/>
+      <c r="K197" s="4"/>
+    </row>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A198" s="3">
         <v>197</v>
       </c>
@@ -3138,8 +3541,10 @@
       <c r="G198" s="3"/>
       <c r="H198" s="3"/>
       <c r="I198" s="3"/>
-    </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J198" s="3"/>
+      <c r="K198" s="3"/>
+    </row>
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199" s="4">
         <v>198</v>
       </c>
@@ -3151,8 +3556,10 @@
       <c r="G199" s="4"/>
       <c r="H199" s="4"/>
       <c r="I199" s="4"/>
-    </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J199" s="4"/>
+      <c r="K199" s="4"/>
+    </row>
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="3">
         <v>199</v>
       </c>
@@ -3164,8 +3571,10 @@
       <c r="G200" s="3"/>
       <c r="H200" s="3"/>
       <c r="I200" s="3"/>
-    </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J200" s="3"/>
+      <c r="K200" s="3"/>
+    </row>
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201" s="4">
         <v>200</v>
       </c>
@@ -3177,8 +3586,10 @@
       <c r="G201" s="4"/>
       <c r="H201" s="4"/>
       <c r="I201" s="4"/>
-    </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J201" s="4"/>
+      <c r="K201" s="4"/>
+    </row>
+    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A202" s="3">
         <v>201</v>
       </c>
@@ -3190,8 +3601,10 @@
       <c r="G202" s="3"/>
       <c r="H202" s="3"/>
       <c r="I202" s="3"/>
-    </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J202" s="3"/>
+      <c r="K202" s="3"/>
+    </row>
+    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203" s="4">
         <v>202</v>
       </c>
@@ -3203,8 +3616,10 @@
       <c r="G203" s="4"/>
       <c r="H203" s="4"/>
       <c r="I203" s="4"/>
-    </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J203" s="4"/>
+      <c r="K203" s="4"/>
+    </row>
+    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A204" s="3">
         <v>203</v>
       </c>
@@ -3216,8 +3631,10 @@
       <c r="G204" s="3"/>
       <c r="H204" s="3"/>
       <c r="I204" s="3"/>
-    </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J204" s="3"/>
+      <c r="K204" s="3"/>
+    </row>
+    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A205" s="4">
         <v>204</v>
       </c>
@@ -3229,8 +3646,10 @@
       <c r="G205" s="4"/>
       <c r="H205" s="4"/>
       <c r="I205" s="4"/>
-    </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J205" s="4"/>
+      <c r="K205" s="4"/>
+    </row>
+    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A206" s="3">
         <v>205</v>
       </c>
@@ -3242,8 +3661,10 @@
       <c r="G206" s="3"/>
       <c r="H206" s="3"/>
       <c r="I206" s="3"/>
-    </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J206" s="3"/>
+      <c r="K206" s="3"/>
+    </row>
+    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A207" s="4">
         <v>206</v>
       </c>
@@ -3255,8 +3676,10 @@
       <c r="G207" s="4"/>
       <c r="H207" s="4"/>
       <c r="I207" s="4"/>
-    </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J207" s="4"/>
+      <c r="K207" s="4"/>
+    </row>
+    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A208" s="3">
         <v>207</v>
       </c>
@@ -3268,8 +3691,10 @@
       <c r="G208" s="3"/>
       <c r="H208" s="3"/>
       <c r="I208" s="3"/>
-    </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J208" s="3"/>
+      <c r="K208" s="3"/>
+    </row>
+    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209" s="4">
         <v>208</v>
       </c>
@@ -3281,8 +3706,10 @@
       <c r="G209" s="4"/>
       <c r="H209" s="4"/>
       <c r="I209" s="4"/>
-    </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J209" s="4"/>
+      <c r="K209" s="4"/>
+    </row>
+    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A210" s="3">
         <v>209</v>
       </c>
@@ -3294,8 +3721,10 @@
       <c r="G210" s="3"/>
       <c r="H210" s="3"/>
       <c r="I210" s="3"/>
-    </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J210" s="3"/>
+      <c r="K210" s="3"/>
+    </row>
+    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A211" s="4">
         <v>210</v>
       </c>
@@ -3307,8 +3736,10 @@
       <c r="G211" s="4"/>
       <c r="H211" s="4"/>
       <c r="I211" s="4"/>
-    </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J211" s="4"/>
+      <c r="K211" s="4"/>
+    </row>
+    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A212" s="3">
         <v>211</v>
       </c>
@@ -3320,8 +3751,10 @@
       <c r="G212" s="3"/>
       <c r="H212" s="3"/>
       <c r="I212" s="3"/>
-    </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J212" s="3"/>
+      <c r="K212" s="3"/>
+    </row>
+    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A213" s="4">
         <v>212</v>
       </c>
@@ -3333,8 +3766,10 @@
       <c r="G213" s="4"/>
       <c r="H213" s="4"/>
       <c r="I213" s="4"/>
-    </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J213" s="4"/>
+      <c r="K213" s="4"/>
+    </row>
+    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A214" s="3">
         <v>213</v>
       </c>
@@ -3346,8 +3781,10 @@
       <c r="G214" s="3"/>
       <c r="H214" s="3"/>
       <c r="I214" s="3"/>
-    </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J214" s="3"/>
+      <c r="K214" s="3"/>
+    </row>
+    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A215" s="4">
         <v>214</v>
       </c>
@@ -3359,8 +3796,10 @@
       <c r="G215" s="4"/>
       <c r="H215" s="4"/>
       <c r="I215" s="4"/>
-    </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J215" s="4"/>
+      <c r="K215" s="4"/>
+    </row>
+    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A216" s="3">
         <v>215</v>
       </c>
@@ -3372,8 +3811,10 @@
       <c r="G216" s="3"/>
       <c r="H216" s="3"/>
       <c r="I216" s="3"/>
-    </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J216" s="3"/>
+      <c r="K216" s="3"/>
+    </row>
+    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A217" s="4">
         <v>216</v>
       </c>
@@ -3385,8 +3826,10 @@
       <c r="G217" s="4"/>
       <c r="H217" s="4"/>
       <c r="I217" s="4"/>
-    </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J217" s="4"/>
+      <c r="K217" s="4"/>
+    </row>
+    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A218" s="3">
         <v>217</v>
       </c>
@@ -3398,8 +3841,10 @@
       <c r="G218" s="3"/>
       <c r="H218" s="3"/>
       <c r="I218" s="3"/>
-    </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J218" s="3"/>
+      <c r="K218" s="3"/>
+    </row>
+    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A219" s="4">
         <v>218</v>
       </c>
@@ -3411,8 +3856,10 @@
       <c r="G219" s="4"/>
       <c r="H219" s="4"/>
       <c r="I219" s="4"/>
-    </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J219" s="4"/>
+      <c r="K219" s="4"/>
+    </row>
+    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A220" s="3">
         <v>219</v>
       </c>
@@ -3424,8 +3871,10 @@
       <c r="G220" s="3"/>
       <c r="H220" s="3"/>
       <c r="I220" s="3"/>
-    </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J220" s="3"/>
+      <c r="K220" s="3"/>
+    </row>
+    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A221" s="4">
         <v>220</v>
       </c>
@@ -3437,8 +3886,10 @@
       <c r="G221" s="4"/>
       <c r="H221" s="4"/>
       <c r="I221" s="4"/>
-    </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J221" s="4"/>
+      <c r="K221" s="4"/>
+    </row>
+    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A222" s="3">
         <v>221</v>
       </c>
@@ -3450,8 +3901,10 @@
       <c r="G222" s="3"/>
       <c r="H222" s="3"/>
       <c r="I222" s="3"/>
-    </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J222" s="3"/>
+      <c r="K222" s="3"/>
+    </row>
+    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A223" s="4">
         <v>222</v>
       </c>
@@ -3463,8 +3916,10 @@
       <c r="G223" s="4"/>
       <c r="H223" s="4"/>
       <c r="I223" s="4"/>
-    </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J223" s="4"/>
+      <c r="K223" s="4"/>
+    </row>
+    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A224" s="3">
         <v>223</v>
       </c>
@@ -3476,8 +3931,10 @@
       <c r="G224" s="3"/>
       <c r="H224" s="3"/>
       <c r="I224" s="3"/>
-    </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J224" s="3"/>
+      <c r="K224" s="3"/>
+    </row>
+    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A225" s="4">
         <v>224</v>
       </c>
@@ -3489,8 +3946,10 @@
       <c r="G225" s="4"/>
       <c r="H225" s="4"/>
       <c r="I225" s="4"/>
-    </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J225" s="4"/>
+      <c r="K225" s="4"/>
+    </row>
+    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A226" s="3">
         <v>225</v>
       </c>
@@ -3502,8 +3961,10 @@
       <c r="G226" s="3"/>
       <c r="H226" s="3"/>
       <c r="I226" s="3"/>
-    </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J226" s="3"/>
+      <c r="K226" s="3"/>
+    </row>
+    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A227" s="4">
         <v>226</v>
       </c>
@@ -3515,8 +3976,10 @@
       <c r="G227" s="4"/>
       <c r="H227" s="4"/>
       <c r="I227" s="4"/>
-    </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J227" s="4"/>
+      <c r="K227" s="4"/>
+    </row>
+    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A228" s="3">
         <v>227</v>
       </c>
@@ -3528,8 +3991,10 @@
       <c r="G228" s="3"/>
       <c r="H228" s="3"/>
       <c r="I228" s="3"/>
-    </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J228" s="3"/>
+      <c r="K228" s="3"/>
+    </row>
+    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A229" s="4">
         <v>228</v>
       </c>
@@ -3541,8 +4006,10 @@
       <c r="G229" s="4"/>
       <c r="H229" s="4"/>
       <c r="I229" s="4"/>
-    </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J229" s="4"/>
+      <c r="K229" s="4"/>
+    </row>
+    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A230" s="3">
         <v>229</v>
       </c>
@@ -3554,8 +4021,10 @@
       <c r="G230" s="3"/>
       <c r="H230" s="3"/>
       <c r="I230" s="3"/>
-    </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J230" s="3"/>
+      <c r="K230" s="3"/>
+    </row>
+    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A231" s="4">
         <v>230</v>
       </c>
@@ -3567,8 +4036,10 @@
       <c r="G231" s="4"/>
       <c r="H231" s="4"/>
       <c r="I231" s="4"/>
-    </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J231" s="4"/>
+      <c r="K231" s="4"/>
+    </row>
+    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A232" s="3">
         <v>231</v>
       </c>
@@ -3580,8 +4051,10 @@
       <c r="G232" s="3"/>
       <c r="H232" s="3"/>
       <c r="I232" s="3"/>
-    </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J232" s="3"/>
+      <c r="K232" s="3"/>
+    </row>
+    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A233" s="4">
         <v>232</v>
       </c>
@@ -3593,8 +4066,10 @@
       <c r="G233" s="4"/>
       <c r="H233" s="4"/>
       <c r="I233" s="4"/>
-    </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J233" s="4"/>
+      <c r="K233" s="4"/>
+    </row>
+    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A234" s="3">
         <v>233</v>
       </c>
@@ -3606,8 +4081,10 @@
       <c r="G234" s="3"/>
       <c r="H234" s="3"/>
       <c r="I234" s="3"/>
-    </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J234" s="3"/>
+      <c r="K234" s="3"/>
+    </row>
+    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A235" s="4">
         <v>234</v>
       </c>
@@ -3619,8 +4096,10 @@
       <c r="G235" s="4"/>
       <c r="H235" s="4"/>
       <c r="I235" s="4"/>
-    </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J235" s="4"/>
+      <c r="K235" s="4"/>
+    </row>
+    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A236" s="3">
         <v>235</v>
       </c>
@@ -3632,8 +4111,10 @@
       <c r="G236" s="3"/>
       <c r="H236" s="3"/>
       <c r="I236" s="3"/>
-    </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J236" s="3"/>
+      <c r="K236" s="3"/>
+    </row>
+    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A237" s="4">
         <v>236</v>
       </c>
@@ -3645,8 +4126,10 @@
       <c r="G237" s="4"/>
       <c r="H237" s="4"/>
       <c r="I237" s="4"/>
-    </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J237" s="4"/>
+      <c r="K237" s="4"/>
+    </row>
+    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A238" s="3">
         <v>237</v>
       </c>
@@ -3658,8 +4141,10 @@
       <c r="G238" s="3"/>
       <c r="H238" s="3"/>
       <c r="I238" s="3"/>
-    </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J238" s="3"/>
+      <c r="K238" s="3"/>
+    </row>
+    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A239" s="4">
         <v>238</v>
       </c>
@@ -3671,8 +4156,10 @@
       <c r="G239" s="4"/>
       <c r="H239" s="4"/>
       <c r="I239" s="4"/>
-    </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J239" s="4"/>
+      <c r="K239" s="4"/>
+    </row>
+    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A240" s="3">
         <v>239</v>
       </c>
@@ -3684,8 +4171,10 @@
       <c r="G240" s="3"/>
       <c r="H240" s="3"/>
       <c r="I240" s="3"/>
-    </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J240" s="3"/>
+      <c r="K240" s="3"/>
+    </row>
+    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A241" s="4">
         <v>240</v>
       </c>
@@ -3697,8 +4186,10 @@
       <c r="G241" s="4"/>
       <c r="H241" s="4"/>
       <c r="I241" s="4"/>
-    </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J241" s="4"/>
+      <c r="K241" s="4"/>
+    </row>
+    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A242" s="3">
         <v>241</v>
       </c>
@@ -3710,8 +4201,10 @@
       <c r="G242" s="3"/>
       <c r="H242" s="3"/>
       <c r="I242" s="3"/>
-    </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J242" s="3"/>
+      <c r="K242" s="3"/>
+    </row>
+    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A243" s="4">
         <v>242</v>
       </c>
@@ -3723,8 +4216,10 @@
       <c r="G243" s="4"/>
       <c r="H243" s="4"/>
       <c r="I243" s="4"/>
-    </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J243" s="4"/>
+      <c r="K243" s="4"/>
+    </row>
+    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A244" s="3">
         <v>243</v>
       </c>
@@ -3736,8 +4231,10 @@
       <c r="G244" s="3"/>
       <c r="H244" s="3"/>
       <c r="I244" s="3"/>
-    </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J244" s="3"/>
+      <c r="K244" s="3"/>
+    </row>
+    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A245" s="4">
         <v>244</v>
       </c>
@@ -3749,8 +4246,10 @@
       <c r="G245" s="4"/>
       <c r="H245" s="4"/>
       <c r="I245" s="4"/>
-    </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J245" s="4"/>
+      <c r="K245" s="4"/>
+    </row>
+    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A246" s="3">
         <v>245</v>
       </c>
@@ -3762,8 +4261,10 @@
       <c r="G246" s="3"/>
       <c r="H246" s="3"/>
       <c r="I246" s="3"/>
-    </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J246" s="3"/>
+      <c r="K246" s="3"/>
+    </row>
+    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A247" s="4">
         <v>246</v>
       </c>
@@ -3775,8 +4276,10 @@
       <c r="G247" s="4"/>
       <c r="H247" s="4"/>
       <c r="I247" s="4"/>
-    </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J247" s="4"/>
+      <c r="K247" s="4"/>
+    </row>
+    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A248" s="3">
         <v>247</v>
       </c>
@@ -3788,8 +4291,10 @@
       <c r="G248" s="3"/>
       <c r="H248" s="3"/>
       <c r="I248" s="3"/>
-    </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J248" s="3"/>
+      <c r="K248" s="3"/>
+    </row>
+    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A249" s="4">
         <v>248</v>
       </c>
@@ -3801,8 +4306,10 @@
       <c r="G249" s="4"/>
       <c r="H249" s="4"/>
       <c r="I249" s="4"/>
-    </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J249" s="4"/>
+      <c r="K249" s="4"/>
+    </row>
+    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A250" s="3">
         <v>249</v>
       </c>
@@ -3814,8 +4321,10 @@
       <c r="G250" s="3"/>
       <c r="H250" s="3"/>
       <c r="I250" s="3"/>
-    </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J250" s="3"/>
+      <c r="K250" s="3"/>
+    </row>
+    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A251" s="4">
         <v>250</v>
       </c>
@@ -3827,8 +4336,10 @@
       <c r="G251" s="4"/>
       <c r="H251" s="4"/>
       <c r="I251" s="4"/>
-    </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J251" s="4"/>
+      <c r="K251" s="4"/>
+    </row>
+    <row r="252" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A252" s="3">
         <v>251</v>
       </c>
@@ -3840,8 +4351,10 @@
       <c r="G252" s="3"/>
       <c r="H252" s="3"/>
       <c r="I252" s="3"/>
-    </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J252" s="3"/>
+      <c r="K252" s="3"/>
+    </row>
+    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A253" s="4">
         <v>252</v>
       </c>
@@ -3853,8 +4366,10 @@
       <c r="G253" s="4"/>
       <c r="H253" s="4"/>
       <c r="I253" s="4"/>
-    </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J253" s="4"/>
+      <c r="K253" s="4"/>
+    </row>
+    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A254" s="3">
         <v>253</v>
       </c>
@@ -3866,8 +4381,10 @@
       <c r="G254" s="3"/>
       <c r="H254" s="3"/>
       <c r="I254" s="3"/>
-    </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J254" s="3"/>
+      <c r="K254" s="3"/>
+    </row>
+    <row r="255" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A255" s="4">
         <v>254</v>
       </c>
@@ -3879,8 +4396,10 @@
       <c r="G255" s="4"/>
       <c r="H255" s="4"/>
       <c r="I255" s="4"/>
-    </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J255" s="4"/>
+      <c r="K255" s="4"/>
+    </row>
+    <row r="256" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A256" s="3">
         <v>255</v>
       </c>
@@ -3892,8 +4411,10 @@
       <c r="G256" s="3"/>
       <c r="H256" s="3"/>
       <c r="I256" s="3"/>
-    </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J256" s="3"/>
+      <c r="K256" s="3"/>
+    </row>
+    <row r="257" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A257" s="4">
         <v>256</v>
       </c>
@@ -3905,8 +4426,10 @@
       <c r="G257" s="4"/>
       <c r="H257" s="4"/>
       <c r="I257" s="4"/>
-    </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J257" s="4"/>
+      <c r="K257" s="4"/>
+    </row>
+    <row r="258" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A258" s="3">
         <v>257</v>
       </c>
@@ -3918,8 +4441,10 @@
       <c r="G258" s="3"/>
       <c r="H258" s="3"/>
       <c r="I258" s="3"/>
-    </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J258" s="3"/>
+      <c r="K258" s="3"/>
+    </row>
+    <row r="259" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A259" s="4">
         <v>258</v>
       </c>
@@ -3931,8 +4456,10 @@
       <c r="G259" s="4"/>
       <c r="H259" s="4"/>
       <c r="I259" s="4"/>
-    </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J259" s="4"/>
+      <c r="K259" s="4"/>
+    </row>
+    <row r="260" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A260" s="3">
         <v>259</v>
       </c>
@@ -3944,8 +4471,10 @@
       <c r="G260" s="3"/>
       <c r="H260" s="3"/>
       <c r="I260" s="3"/>
-    </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J260" s="3"/>
+      <c r="K260" s="3"/>
+    </row>
+    <row r="261" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A261" s="4">
         <v>260</v>
       </c>
@@ -3957,8 +4486,10 @@
       <c r="G261" s="4"/>
       <c r="H261" s="4"/>
       <c r="I261" s="4"/>
-    </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J261" s="4"/>
+      <c r="K261" s="4"/>
+    </row>
+    <row r="262" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A262" s="3">
         <v>261</v>
       </c>
@@ -3970,8 +4501,10 @@
       <c r="G262" s="3"/>
       <c r="H262" s="3"/>
       <c r="I262" s="3"/>
-    </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J262" s="3"/>
+      <c r="K262" s="3"/>
+    </row>
+    <row r="263" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A263" s="4">
         <v>262</v>
       </c>
@@ -3983,8 +4516,10 @@
       <c r="G263" s="4"/>
       <c r="H263" s="4"/>
       <c r="I263" s="4"/>
-    </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J263" s="4"/>
+      <c r="K263" s="4"/>
+    </row>
+    <row r="264" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A264" s="3">
         <v>263</v>
       </c>
@@ -3996,8 +4531,10 @@
       <c r="G264" s="3"/>
       <c r="H264" s="3"/>
       <c r="I264" s="3"/>
-    </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J264" s="3"/>
+      <c r="K264" s="3"/>
+    </row>
+    <row r="265" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A265" s="4">
         <v>264</v>
       </c>
@@ -4009,8 +4546,10 @@
       <c r="G265" s="4"/>
       <c r="H265" s="4"/>
       <c r="I265" s="4"/>
-    </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J265" s="4"/>
+      <c r="K265" s="4"/>
+    </row>
+    <row r="266" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A266" s="3">
         <v>265</v>
       </c>
@@ -4022,8 +4561,10 @@
       <c r="G266" s="3"/>
       <c r="H266" s="3"/>
       <c r="I266" s="3"/>
-    </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J266" s="3"/>
+      <c r="K266" s="3"/>
+    </row>
+    <row r="267" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A267" s="4">
         <v>266</v>
       </c>
@@ -4035,8 +4576,10 @@
       <c r="G267" s="4"/>
       <c r="H267" s="4"/>
       <c r="I267" s="4"/>
-    </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J267" s="4"/>
+      <c r="K267" s="4"/>
+    </row>
+    <row r="268" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A268" s="3">
         <v>267</v>
       </c>
@@ -4048,8 +4591,10 @@
       <c r="G268" s="3"/>
       <c r="H268" s="3"/>
       <c r="I268" s="3"/>
-    </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J268" s="3"/>
+      <c r="K268" s="3"/>
+    </row>
+    <row r="269" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A269" s="4">
         <v>268</v>
       </c>
@@ -4061,8 +4606,10 @@
       <c r="G269" s="4"/>
       <c r="H269" s="4"/>
       <c r="I269" s="4"/>
-    </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J269" s="4"/>
+      <c r="K269" s="4"/>
+    </row>
+    <row r="270" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A270" s="3">
         <v>269</v>
       </c>
@@ -4074,8 +4621,10 @@
       <c r="G270" s="3"/>
       <c r="H270" s="3"/>
       <c r="I270" s="3"/>
-    </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J270" s="3"/>
+      <c r="K270" s="3"/>
+    </row>
+    <row r="271" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A271" s="4">
         <v>270</v>
       </c>
@@ -4087,8 +4636,10 @@
       <c r="G271" s="4"/>
       <c r="H271" s="4"/>
       <c r="I271" s="4"/>
-    </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J271" s="4"/>
+      <c r="K271" s="4"/>
+    </row>
+    <row r="272" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A272" s="3">
         <v>271</v>
       </c>
@@ -4100,8 +4651,10 @@
       <c r="G272" s="3"/>
       <c r="H272" s="3"/>
       <c r="I272" s="3"/>
-    </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J272" s="3"/>
+      <c r="K272" s="3"/>
+    </row>
+    <row r="273" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A273" s="4">
         <v>272</v>
       </c>
@@ -4113,8 +4666,10 @@
       <c r="G273" s="4"/>
       <c r="H273" s="4"/>
       <c r="I273" s="4"/>
-    </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J273" s="4"/>
+      <c r="K273" s="4"/>
+    </row>
+    <row r="274" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A274" s="3">
         <v>273</v>
       </c>
@@ -4126,8 +4681,10 @@
       <c r="G274" s="3"/>
       <c r="H274" s="3"/>
       <c r="I274" s="3"/>
-    </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J274" s="3"/>
+      <c r="K274" s="3"/>
+    </row>
+    <row r="275" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A275" s="4">
         <v>274</v>
       </c>
@@ -4139,8 +4696,10 @@
       <c r="G275" s="4"/>
       <c r="H275" s="4"/>
       <c r="I275" s="4"/>
-    </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J275" s="4"/>
+      <c r="K275" s="4"/>
+    </row>
+    <row r="276" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A276" s="3">
         <v>275</v>
       </c>
@@ -4152,8 +4711,10 @@
       <c r="G276" s="3"/>
       <c r="H276" s="3"/>
       <c r="I276" s="3"/>
-    </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J276" s="3"/>
+      <c r="K276" s="3"/>
+    </row>
+    <row r="277" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A277" s="4">
         <v>276</v>
       </c>
@@ -4165,8 +4726,10 @@
       <c r="G277" s="4"/>
       <c r="H277" s="4"/>
       <c r="I277" s="4"/>
-    </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J277" s="4"/>
+      <c r="K277" s="4"/>
+    </row>
+    <row r="278" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A278" s="3">
         <v>277</v>
       </c>
@@ -4178,8 +4741,10 @@
       <c r="G278" s="3"/>
       <c r="H278" s="3"/>
       <c r="I278" s="3"/>
-    </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J278" s="3"/>
+      <c r="K278" s="3"/>
+    </row>
+    <row r="279" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A279" s="4">
         <v>278</v>
       </c>
@@ -4191,8 +4756,10 @@
       <c r="G279" s="4"/>
       <c r="H279" s="4"/>
       <c r="I279" s="4"/>
-    </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J279" s="4"/>
+      <c r="K279" s="4"/>
+    </row>
+    <row r="280" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A280" s="3">
         <v>279</v>
       </c>
@@ -4204,8 +4771,10 @@
       <c r="G280" s="3"/>
       <c r="H280" s="3"/>
       <c r="I280" s="3"/>
-    </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J280" s="3"/>
+      <c r="K280" s="3"/>
+    </row>
+    <row r="281" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A281" s="4">
         <v>280</v>
       </c>
@@ -4217,8 +4786,10 @@
       <c r="G281" s="4"/>
       <c r="H281" s="4"/>
       <c r="I281" s="4"/>
-    </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J281" s="4"/>
+      <c r="K281" s="4"/>
+    </row>
+    <row r="282" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A282" s="3">
         <v>281</v>
       </c>
@@ -4230,8 +4801,10 @@
       <c r="G282" s="3"/>
       <c r="H282" s="3"/>
       <c r="I282" s="3"/>
-    </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J282" s="3"/>
+      <c r="K282" s="3"/>
+    </row>
+    <row r="283" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A283" s="4">
         <v>282</v>
       </c>
@@ -4243,8 +4816,10 @@
       <c r="G283" s="4"/>
       <c r="H283" s="4"/>
       <c r="I283" s="4"/>
-    </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J283" s="4"/>
+      <c r="K283" s="4"/>
+    </row>
+    <row r="284" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A284" s="3">
         <v>283</v>
       </c>
@@ -4256,8 +4831,10 @@
       <c r="G284" s="3"/>
       <c r="H284" s="3"/>
       <c r="I284" s="3"/>
-    </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J284" s="3"/>
+      <c r="K284" s="3"/>
+    </row>
+    <row r="285" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A285" s="4">
         <v>284</v>
       </c>
@@ -4269,8 +4846,10 @@
       <c r="G285" s="4"/>
       <c r="H285" s="4"/>
       <c r="I285" s="4"/>
-    </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J285" s="4"/>
+      <c r="K285" s="4"/>
+    </row>
+    <row r="286" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A286" s="3">
         <v>285</v>
       </c>
@@ -4282,8 +4861,10 @@
       <c r="G286" s="3"/>
       <c r="H286" s="3"/>
       <c r="I286" s="3"/>
-    </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J286" s="3"/>
+      <c r="K286" s="3"/>
+    </row>
+    <row r="287" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A287" s="4">
         <v>286</v>
       </c>
@@ -4295,8 +4876,10 @@
       <c r="G287" s="4"/>
       <c r="H287" s="4"/>
       <c r="I287" s="4"/>
-    </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J287" s="4"/>
+      <c r="K287" s="4"/>
+    </row>
+    <row r="288" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A288" s="3">
         <v>287</v>
       </c>
@@ -4308,8 +4891,10 @@
       <c r="G288" s="3"/>
       <c r="H288" s="3"/>
       <c r="I288" s="3"/>
-    </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J288" s="3"/>
+      <c r="K288" s="3"/>
+    </row>
+    <row r="289" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A289" s="4">
         <v>288</v>
       </c>
@@ -4321,8 +4906,10 @@
       <c r="G289" s="4"/>
       <c r="H289" s="4"/>
       <c r="I289" s="4"/>
-    </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J289" s="4"/>
+      <c r="K289" s="4"/>
+    </row>
+    <row r="290" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A290" s="3">
         <v>289</v>
       </c>
@@ -4334,8 +4921,10 @@
       <c r="G290" s="3"/>
       <c r="H290" s="3"/>
       <c r="I290" s="3"/>
-    </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J290" s="3"/>
+      <c r="K290" s="3"/>
+    </row>
+    <row r="291" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A291" s="4">
         <v>290</v>
       </c>
@@ -4347,8 +4936,10 @@
       <c r="G291" s="4"/>
       <c r="H291" s="4"/>
       <c r="I291" s="4"/>
-    </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J291" s="4"/>
+      <c r="K291" s="4"/>
+    </row>
+    <row r="292" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A292" s="3">
         <v>291</v>
       </c>
@@ -4360,8 +4951,10 @@
       <c r="G292" s="3"/>
       <c r="H292" s="3"/>
       <c r="I292" s="3"/>
-    </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J292" s="3"/>
+      <c r="K292" s="3"/>
+    </row>
+    <row r="293" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A293" s="4">
         <v>292</v>
       </c>
@@ -4373,8 +4966,10 @@
       <c r="G293" s="4"/>
       <c r="H293" s="4"/>
       <c r="I293" s="4"/>
-    </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J293" s="4"/>
+      <c r="K293" s="4"/>
+    </row>
+    <row r="294" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A294" s="3">
         <v>293</v>
       </c>
@@ -4386,8 +4981,10 @@
       <c r="G294" s="3"/>
       <c r="H294" s="3"/>
       <c r="I294" s="3"/>
-    </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J294" s="3"/>
+      <c r="K294" s="3"/>
+    </row>
+    <row r="295" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A295" s="4">
         <v>294</v>
       </c>
@@ -4399,8 +4996,10 @@
       <c r="G295" s="4"/>
       <c r="H295" s="4"/>
       <c r="I295" s="4"/>
-    </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J295" s="4"/>
+      <c r="K295" s="4"/>
+    </row>
+    <row r="296" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A296" s="3">
         <v>295</v>
       </c>
@@ -4412,8 +5011,10 @@
       <c r="G296" s="3"/>
       <c r="H296" s="3"/>
       <c r="I296" s="3"/>
-    </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J296" s="3"/>
+      <c r="K296" s="3"/>
+    </row>
+    <row r="297" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A297" s="4">
         <v>296</v>
       </c>
@@ -4425,8 +5026,10 @@
       <c r="G297" s="4"/>
       <c r="H297" s="4"/>
       <c r="I297" s="4"/>
-    </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J297" s="4"/>
+      <c r="K297" s="4"/>
+    </row>
+    <row r="298" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A298" s="3">
         <v>297</v>
       </c>
@@ -4438,8 +5041,10 @@
       <c r="G298" s="3"/>
       <c r="H298" s="3"/>
       <c r="I298" s="3"/>
-    </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J298" s="3"/>
+      <c r="K298" s="3"/>
+    </row>
+    <row r="299" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A299" s="4">
         <v>298</v>
       </c>
@@ -4451,8 +5056,10 @@
       <c r="G299" s="4"/>
       <c r="H299" s="4"/>
       <c r="I299" s="4"/>
-    </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J299" s="4"/>
+      <c r="K299" s="4"/>
+    </row>
+    <row r="300" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A300" s="3">
         <v>299</v>
       </c>
@@ -4464,8 +5071,10 @@
       <c r="G300" s="3"/>
       <c r="H300" s="3"/>
       <c r="I300" s="3"/>
-    </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J300" s="3"/>
+      <c r="K300" s="3"/>
+    </row>
+    <row r="301" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A301" s="4">
         <v>300</v>
       </c>
@@ -4477,8 +5086,10 @@
       <c r="G301" s="4"/>
       <c r="H301" s="4"/>
       <c r="I301" s="4"/>
-    </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J301" s="4"/>
+      <c r="K301" s="4"/>
+    </row>
+    <row r="302" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A302" s="3">
         <v>301</v>
       </c>
@@ -4490,8 +5101,10 @@
       <c r="G302" s="3"/>
       <c r="H302" s="3"/>
       <c r="I302" s="3"/>
-    </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J302" s="3"/>
+      <c r="K302" s="3"/>
+    </row>
+    <row r="303" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A303" s="4">
         <v>302</v>
       </c>
@@ -4503,8 +5116,10 @@
       <c r="G303" s="4"/>
       <c r="H303" s="4"/>
       <c r="I303" s="4"/>
-    </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J303" s="4"/>
+      <c r="K303" s="4"/>
+    </row>
+    <row r="304" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A304" s="3">
         <v>303</v>
       </c>
@@ -4516,8 +5131,10 @@
       <c r="G304" s="3"/>
       <c r="H304" s="3"/>
       <c r="I304" s="3"/>
-    </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J304" s="3"/>
+      <c r="K304" s="3"/>
+    </row>
+    <row r="305" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A305" s="4">
         <v>304</v>
       </c>
@@ -4529,8 +5146,10 @@
       <c r="G305" s="4"/>
       <c r="H305" s="4"/>
       <c r="I305" s="4"/>
-    </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J305" s="4"/>
+      <c r="K305" s="4"/>
+    </row>
+    <row r="306" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A306" s="3">
         <v>305</v>
       </c>
@@ -4542,8 +5161,10 @@
       <c r="G306" s="3"/>
       <c r="H306" s="3"/>
       <c r="I306" s="3"/>
-    </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J306" s="3"/>
+      <c r="K306" s="3"/>
+    </row>
+    <row r="307" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A307" s="4">
         <v>306</v>
       </c>
@@ -4555,8 +5176,10 @@
       <c r="G307" s="4"/>
       <c r="H307" s="4"/>
       <c r="I307" s="4"/>
-    </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J307" s="4"/>
+      <c r="K307" s="4"/>
+    </row>
+    <row r="308" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A308" s="3">
         <v>307</v>
       </c>
@@ -4568,8 +5191,10 @@
       <c r="G308" s="3"/>
       <c r="H308" s="3"/>
       <c r="I308" s="3"/>
-    </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J308" s="3"/>
+      <c r="K308" s="3"/>
+    </row>
+    <row r="309" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A309" s="4">
         <v>308</v>
       </c>
@@ -4581,8 +5206,10 @@
       <c r="G309" s="4"/>
       <c r="H309" s="4"/>
       <c r="I309" s="4"/>
-    </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J309" s="4"/>
+      <c r="K309" s="4"/>
+    </row>
+    <row r="310" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A310" s="3">
         <v>309</v>
       </c>
@@ -4594,8 +5221,10 @@
       <c r="G310" s="3"/>
       <c r="H310" s="3"/>
       <c r="I310" s="3"/>
-    </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J310" s="3"/>
+      <c r="K310" s="3"/>
+    </row>
+    <row r="311" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A311" s="4">
         <v>310</v>
       </c>
@@ -4607,8 +5236,10 @@
       <c r="G311" s="4"/>
       <c r="H311" s="4"/>
       <c r="I311" s="4"/>
-    </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J311" s="4"/>
+      <c r="K311" s="4"/>
+    </row>
+    <row r="312" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A312" s="3">
         <v>311</v>
       </c>
@@ -4620,8 +5251,10 @@
       <c r="G312" s="3"/>
       <c r="H312" s="3"/>
       <c r="I312" s="3"/>
-    </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J312" s="3"/>
+      <c r="K312" s="3"/>
+    </row>
+    <row r="313" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A313" s="4">
         <v>312</v>
       </c>
@@ -4633,8 +5266,10 @@
       <c r="G313" s="4"/>
       <c r="H313" s="4"/>
       <c r="I313" s="4"/>
-    </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J313" s="4"/>
+      <c r="K313" s="4"/>
+    </row>
+    <row r="314" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A314" s="3">
         <v>313</v>
       </c>
@@ -4646,8 +5281,10 @@
       <c r="G314" s="3"/>
       <c r="H314" s="3"/>
       <c r="I314" s="3"/>
-    </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J314" s="3"/>
+      <c r="K314" s="3"/>
+    </row>
+    <row r="315" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A315" s="4">
         <v>314</v>
       </c>
@@ -4659,8 +5296,10 @@
       <c r="G315" s="4"/>
       <c r="H315" s="4"/>
       <c r="I315" s="4"/>
-    </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J315" s="4"/>
+      <c r="K315" s="4"/>
+    </row>
+    <row r="316" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A316" s="3">
         <v>315</v>
       </c>
@@ -4672,8 +5311,10 @@
       <c r="G316" s="3"/>
       <c r="H316" s="3"/>
       <c r="I316" s="3"/>
-    </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J316" s="3"/>
+      <c r="K316" s="3"/>
+    </row>
+    <row r="317" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A317" s="4">
         <v>316</v>
       </c>
@@ -4685,8 +5326,10 @@
       <c r="G317" s="4"/>
       <c r="H317" s="4"/>
       <c r="I317" s="4"/>
-    </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J317" s="4"/>
+      <c r="K317" s="4"/>
+    </row>
+    <row r="318" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A318" s="3">
         <v>317</v>
       </c>
@@ -4698,8 +5341,10 @@
       <c r="G318" s="3"/>
       <c r="H318" s="3"/>
       <c r="I318" s="3"/>
-    </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J318" s="3"/>
+      <c r="K318" s="3"/>
+    </row>
+    <row r="319" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A319" s="4">
         <v>318</v>
       </c>
@@ -4711,8 +5356,10 @@
       <c r="G319" s="4"/>
       <c r="H319" s="4"/>
       <c r="I319" s="4"/>
-    </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J319" s="4"/>
+      <c r="K319" s="4"/>
+    </row>
+    <row r="320" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A320" s="3">
         <v>319</v>
       </c>
@@ -4724,8 +5371,10 @@
       <c r="G320" s="3"/>
       <c r="H320" s="3"/>
       <c r="I320" s="3"/>
-    </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J320" s="3"/>
+      <c r="K320" s="3"/>
+    </row>
+    <row r="321" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A321" s="4">
         <v>320</v>
       </c>
@@ -4737,8 +5386,10 @@
       <c r="G321" s="4"/>
       <c r="H321" s="4"/>
       <c r="I321" s="4"/>
-    </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J321" s="4"/>
+      <c r="K321" s="4"/>
+    </row>
+    <row r="322" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A322" s="3">
         <v>321</v>
       </c>
@@ -4750,8 +5401,10 @@
       <c r="G322" s="3"/>
       <c r="H322" s="3"/>
       <c r="I322" s="3"/>
-    </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J322" s="3"/>
+      <c r="K322" s="3"/>
+    </row>
+    <row r="323" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A323" s="4">
         <v>322</v>
       </c>
@@ -4763,8 +5416,10 @@
       <c r="G323" s="4"/>
       <c r="H323" s="4"/>
       <c r="I323" s="4"/>
-    </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J323" s="4"/>
+      <c r="K323" s="4"/>
+    </row>
+    <row r="324" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A324" s="3">
         <v>323</v>
       </c>
@@ -4776,8 +5431,10 @@
       <c r="G324" s="3"/>
       <c r="H324" s="3"/>
       <c r="I324" s="3"/>
-    </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J324" s="3"/>
+      <c r="K324" s="3"/>
+    </row>
+    <row r="325" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A325" s="4">
         <v>324</v>
       </c>
@@ -4789,8 +5446,10 @@
       <c r="G325" s="4"/>
       <c r="H325" s="4"/>
       <c r="I325" s="4"/>
-    </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J325" s="4"/>
+      <c r="K325" s="4"/>
+    </row>
+    <row r="326" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A326" s="3">
         <v>325</v>
       </c>
@@ -4802,8 +5461,10 @@
       <c r="G326" s="3"/>
       <c r="H326" s="3"/>
       <c r="I326" s="3"/>
-    </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J326" s="3"/>
+      <c r="K326" s="3"/>
+    </row>
+    <row r="327" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A327" s="4">
         <v>326</v>
       </c>
@@ -4815,8 +5476,10 @@
       <c r="G327" s="4"/>
       <c r="H327" s="4"/>
       <c r="I327" s="4"/>
-    </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J327" s="4"/>
+      <c r="K327" s="4"/>
+    </row>
+    <row r="328" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A328" s="3">
         <v>327</v>
       </c>
@@ -4828,8 +5491,10 @@
       <c r="G328" s="3"/>
       <c r="H328" s="3"/>
       <c r="I328" s="3"/>
-    </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J328" s="3"/>
+      <c r="K328" s="3"/>
+    </row>
+    <row r="329" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A329" s="4">
         <v>328</v>
       </c>
@@ -4841,8 +5506,10 @@
       <c r="G329" s="4"/>
       <c r="H329" s="4"/>
       <c r="I329" s="4"/>
-    </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J329" s="4"/>
+      <c r="K329" s="4"/>
+    </row>
+    <row r="330" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A330" s="3">
         <v>329</v>
       </c>
@@ -4854,8 +5521,10 @@
       <c r="G330" s="3"/>
       <c r="H330" s="3"/>
       <c r="I330" s="3"/>
-    </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J330" s="3"/>
+      <c r="K330" s="3"/>
+    </row>
+    <row r="331" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A331" s="4">
         <v>330</v>
       </c>
@@ -4867,8 +5536,10 @@
       <c r="G331" s="4"/>
       <c r="H331" s="4"/>
       <c r="I331" s="4"/>
-    </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J331" s="4"/>
+      <c r="K331" s="4"/>
+    </row>
+    <row r="332" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A332" s="3">
         <v>331</v>
       </c>
@@ -4880,8 +5551,10 @@
       <c r="G332" s="3"/>
       <c r="H332" s="3"/>
       <c r="I332" s="3"/>
-    </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J332" s="3"/>
+      <c r="K332" s="3"/>
+    </row>
+    <row r="333" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A333" s="4">
         <v>332</v>
       </c>
@@ -4893,8 +5566,10 @@
       <c r="G333" s="4"/>
       <c r="H333" s="4"/>
       <c r="I333" s="4"/>
-    </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J333" s="4"/>
+      <c r="K333" s="4"/>
+    </row>
+    <row r="334" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A334" s="3">
         <v>333</v>
       </c>
@@ -4906,8 +5581,10 @@
       <c r="G334" s="3"/>
       <c r="H334" s="3"/>
       <c r="I334" s="3"/>
-    </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J334" s="3"/>
+      <c r="K334" s="3"/>
+    </row>
+    <row r="335" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A335" s="4">
         <v>334</v>
       </c>
@@ -4919,8 +5596,10 @@
       <c r="G335" s="4"/>
       <c r="H335" s="4"/>
       <c r="I335" s="4"/>
-    </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J335" s="4"/>
+      <c r="K335" s="4"/>
+    </row>
+    <row r="336" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A336" s="3">
         <v>335</v>
       </c>
@@ -4932,8 +5611,10 @@
       <c r="G336" s="3"/>
       <c r="H336" s="3"/>
       <c r="I336" s="3"/>
-    </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J336" s="3"/>
+      <c r="K336" s="3"/>
+    </row>
+    <row r="337" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A337" s="4">
         <v>336</v>
       </c>
@@ -4945,8 +5626,10 @@
       <c r="G337" s="4"/>
       <c r="H337" s="4"/>
       <c r="I337" s="4"/>
-    </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J337" s="4"/>
+      <c r="K337" s="4"/>
+    </row>
+    <row r="338" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A338" s="3">
         <v>337</v>
       </c>
@@ -4958,8 +5641,10 @@
       <c r="G338" s="3"/>
       <c r="H338" s="3"/>
       <c r="I338" s="3"/>
-    </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J338" s="3"/>
+      <c r="K338" s="3"/>
+    </row>
+    <row r="339" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A339" s="4">
         <v>338</v>
       </c>
@@ -4971,8 +5656,10 @@
       <c r="G339" s="4"/>
       <c r="H339" s="4"/>
       <c r="I339" s="4"/>
-    </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J339" s="4"/>
+      <c r="K339" s="4"/>
+    </row>
+    <row r="340" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A340" s="3">
         <v>339</v>
       </c>
@@ -4984,8 +5671,10 @@
       <c r="G340" s="3"/>
       <c r="H340" s="3"/>
       <c r="I340" s="3"/>
-    </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J340" s="3"/>
+      <c r="K340" s="3"/>
+    </row>
+    <row r="341" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A341" s="4">
         <v>340</v>
       </c>
@@ -4997,8 +5686,10 @@
       <c r="G341" s="4"/>
       <c r="H341" s="4"/>
       <c r="I341" s="4"/>
-    </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J341" s="4"/>
+      <c r="K341" s="4"/>
+    </row>
+    <row r="342" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A342" s="3">
         <v>341</v>
       </c>
@@ -5010,8 +5701,10 @@
       <c r="G342" s="3"/>
       <c r="H342" s="3"/>
       <c r="I342" s="3"/>
-    </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J342" s="3"/>
+      <c r="K342" s="3"/>
+    </row>
+    <row r="343" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A343" s="4">
         <v>342</v>
       </c>
@@ -5023,8 +5716,10 @@
       <c r="G343" s="4"/>
       <c r="H343" s="4"/>
       <c r="I343" s="4"/>
-    </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J343" s="4"/>
+      <c r="K343" s="4"/>
+    </row>
+    <row r="344" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A344" s="3">
         <v>343</v>
       </c>
@@ -5036,8 +5731,10 @@
       <c r="G344" s="3"/>
       <c r="H344" s="3"/>
       <c r="I344" s="3"/>
-    </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J344" s="3"/>
+      <c r="K344" s="3"/>
+    </row>
+    <row r="345" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A345" s="4">
         <v>344</v>
       </c>
@@ -5049,8 +5746,10 @@
       <c r="G345" s="4"/>
       <c r="H345" s="4"/>
       <c r="I345" s="4"/>
-    </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J345" s="4"/>
+      <c r="K345" s="4"/>
+    </row>
+    <row r="346" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A346" s="3">
         <v>345</v>
       </c>
@@ -5062,8 +5761,10 @@
       <c r="G346" s="3"/>
       <c r="H346" s="3"/>
       <c r="I346" s="3"/>
-    </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J346" s="3"/>
+      <c r="K346" s="3"/>
+    </row>
+    <row r="347" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A347" s="4">
         <v>346</v>
       </c>
@@ -5075,8 +5776,10 @@
       <c r="G347" s="4"/>
       <c r="H347" s="4"/>
       <c r="I347" s="4"/>
-    </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J347" s="4"/>
+      <c r="K347" s="4"/>
+    </row>
+    <row r="348" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A348" s="3">
         <v>347</v>
       </c>
@@ -5088,8 +5791,10 @@
       <c r="G348" s="3"/>
       <c r="H348" s="3"/>
       <c r="I348" s="3"/>
-    </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J348" s="3"/>
+      <c r="K348" s="3"/>
+    </row>
+    <row r="349" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A349" s="4">
         <v>348</v>
       </c>
@@ -5101,8 +5806,10 @@
       <c r="G349" s="4"/>
       <c r="H349" s="4"/>
       <c r="I349" s="4"/>
-    </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J349" s="4"/>
+      <c r="K349" s="4"/>
+    </row>
+    <row r="350" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A350" s="3">
         <v>349</v>
       </c>
@@ -5114,8 +5821,10 @@
       <c r="G350" s="3"/>
       <c r="H350" s="3"/>
       <c r="I350" s="3"/>
-    </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J350" s="3"/>
+      <c r="K350" s="3"/>
+    </row>
+    <row r="351" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A351" s="4">
         <v>350</v>
       </c>
@@ -5127,8 +5836,10 @@
       <c r="G351" s="4"/>
       <c r="H351" s="4"/>
       <c r="I351" s="4"/>
-    </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J351" s="4"/>
+      <c r="K351" s="4"/>
+    </row>
+    <row r="352" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A352" s="3">
         <v>351</v>
       </c>
@@ -5140,8 +5851,10 @@
       <c r="G352" s="3"/>
       <c r="H352" s="3"/>
       <c r="I352" s="3"/>
-    </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J352" s="3"/>
+      <c r="K352" s="3"/>
+    </row>
+    <row r="353" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A353" s="4">
         <v>352</v>
       </c>
@@ -5153,8 +5866,10 @@
       <c r="G353" s="4"/>
       <c r="H353" s="4"/>
       <c r="I353" s="4"/>
-    </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J353" s="4"/>
+      <c r="K353" s="4"/>
+    </row>
+    <row r="354" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A354" s="3">
         <v>353</v>
       </c>
@@ -5166,8 +5881,10 @@
       <c r="G354" s="3"/>
       <c r="H354" s="3"/>
       <c r="I354" s="3"/>
-    </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J354" s="3"/>
+      <c r="K354" s="3"/>
+    </row>
+    <row r="355" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A355" s="4">
         <v>354</v>
       </c>
@@ -5179,8 +5896,10 @@
       <c r="G355" s="4"/>
       <c r="H355" s="4"/>
       <c r="I355" s="4"/>
-    </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J355" s="4"/>
+      <c r="K355" s="4"/>
+    </row>
+    <row r="356" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A356" s="3">
         <v>355</v>
       </c>
@@ -5192,8 +5911,10 @@
       <c r="G356" s="3"/>
       <c r="H356" s="3"/>
       <c r="I356" s="3"/>
-    </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J356" s="3"/>
+      <c r="K356" s="3"/>
+    </row>
+    <row r="357" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A357" s="4">
         <v>356</v>
       </c>
@@ -5205,8 +5926,10 @@
       <c r="G357" s="4"/>
       <c r="H357" s="4"/>
       <c r="I357" s="4"/>
-    </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J357" s="4"/>
+      <c r="K357" s="4"/>
+    </row>
+    <row r="358" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A358" s="3">
         <v>357</v>
       </c>
@@ -5218,8 +5941,10 @@
       <c r="G358" s="3"/>
       <c r="H358" s="3"/>
       <c r="I358" s="3"/>
-    </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J358" s="3"/>
+      <c r="K358" s="3"/>
+    </row>
+    <row r="359" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A359" s="4">
         <v>358</v>
       </c>
@@ -5231,8 +5956,10 @@
       <c r="G359" s="4"/>
       <c r="H359" s="4"/>
       <c r="I359" s="4"/>
-    </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J359" s="4"/>
+      <c r="K359" s="4"/>
+    </row>
+    <row r="360" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A360" s="3">
         <v>359</v>
       </c>
@@ -5244,8 +5971,10 @@
       <c r="G360" s="3"/>
       <c r="H360" s="3"/>
       <c r="I360" s="3"/>
-    </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J360" s="3"/>
+      <c r="K360" s="3"/>
+    </row>
+    <row r="361" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A361" s="4">
         <v>360</v>
       </c>
@@ -5257,8 +5986,10 @@
       <c r="G361" s="4"/>
       <c r="H361" s="4"/>
       <c r="I361" s="4"/>
-    </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J361" s="4"/>
+      <c r="K361" s="4"/>
+    </row>
+    <row r="362" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A362" s="3">
         <v>361</v>
       </c>
@@ -5270,8 +6001,10 @@
       <c r="G362" s="3"/>
       <c r="H362" s="3"/>
       <c r="I362" s="3"/>
-    </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J362" s="3"/>
+      <c r="K362" s="3"/>
+    </row>
+    <row r="363" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A363" s="4">
         <v>362</v>
       </c>
@@ -5283,8 +6016,10 @@
       <c r="G363" s="4"/>
       <c r="H363" s="4"/>
       <c r="I363" s="4"/>
-    </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J363" s="4"/>
+      <c r="K363" s="4"/>
+    </row>
+    <row r="364" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A364" s="3">
         <v>363</v>
       </c>
@@ -5296,8 +6031,10 @@
       <c r="G364" s="3"/>
       <c r="H364" s="3"/>
       <c r="I364" s="3"/>
-    </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J364" s="3"/>
+      <c r="K364" s="3"/>
+    </row>
+    <row r="365" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A365" s="4">
         <v>364</v>
       </c>
@@ -5309,8 +6046,10 @@
       <c r="G365" s="4"/>
       <c r="H365" s="4"/>
       <c r="I365" s="4"/>
-    </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J365" s="4"/>
+      <c r="K365" s="4"/>
+    </row>
+    <row r="366" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A366" s="3">
         <v>365</v>
       </c>
@@ -5322,8 +6061,10 @@
       <c r="G366" s="3"/>
       <c r="H366" s="3"/>
       <c r="I366" s="3"/>
-    </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J366" s="3"/>
+      <c r="K366" s="3"/>
+    </row>
+    <row r="367" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A367" s="4">
         <v>366</v>
       </c>
@@ -5335,8 +6076,10 @@
       <c r="G367" s="4"/>
       <c r="H367" s="4"/>
       <c r="I367" s="4"/>
-    </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J367" s="4"/>
+      <c r="K367" s="4"/>
+    </row>
+    <row r="368" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A368" s="3">
         <v>367</v>
       </c>
@@ -5348,8 +6091,10 @@
       <c r="G368" s="3"/>
       <c r="H368" s="3"/>
       <c r="I368" s="3"/>
-    </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J368" s="3"/>
+      <c r="K368" s="3"/>
+    </row>
+    <row r="369" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A369" s="4">
         <v>368</v>
       </c>
@@ -5361,8 +6106,10 @@
       <c r="G369" s="4"/>
       <c r="H369" s="4"/>
       <c r="I369" s="4"/>
-    </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J369" s="4"/>
+      <c r="K369" s="4"/>
+    </row>
+    <row r="370" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A370" s="3">
         <v>369</v>
       </c>
@@ -5374,8 +6121,10 @@
       <c r="G370" s="3"/>
       <c r="H370" s="3"/>
       <c r="I370" s="3"/>
-    </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J370" s="3"/>
+      <c r="K370" s="3"/>
+    </row>
+    <row r="371" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A371" s="4">
         <v>370</v>
       </c>
@@ -5387,8 +6136,10 @@
       <c r="G371" s="4"/>
       <c r="H371" s="4"/>
       <c r="I371" s="4"/>
-    </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J371" s="4"/>
+      <c r="K371" s="4"/>
+    </row>
+    <row r="372" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A372" s="3">
         <v>371</v>
       </c>
@@ -5400,8 +6151,10 @@
       <c r="G372" s="3"/>
       <c r="H372" s="3"/>
       <c r="I372" s="3"/>
-    </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J372" s="3"/>
+      <c r="K372" s="3"/>
+    </row>
+    <row r="373" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A373" s="4">
         <v>372</v>
       </c>
@@ -5413,8 +6166,10 @@
       <c r="G373" s="4"/>
       <c r="H373" s="4"/>
       <c r="I373" s="4"/>
-    </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J373" s="4"/>
+      <c r="K373" s="4"/>
+    </row>
+    <row r="374" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A374" s="3">
         <v>373</v>
       </c>
@@ -5426,8 +6181,10 @@
       <c r="G374" s="3"/>
       <c r="H374" s="3"/>
       <c r="I374" s="3"/>
-    </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J374" s="3"/>
+      <c r="K374" s="3"/>
+    </row>
+    <row r="375" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A375" s="4">
         <v>374</v>
       </c>
@@ -5439,8 +6196,10 @@
       <c r="G375" s="4"/>
       <c r="H375" s="4"/>
       <c r="I375" s="4"/>
-    </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J375" s="4"/>
+      <c r="K375" s="4"/>
+    </row>
+    <row r="376" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A376" s="3">
         <v>375</v>
       </c>
@@ -5452,8 +6211,10 @@
       <c r="G376" s="3"/>
       <c r="H376" s="3"/>
       <c r="I376" s="3"/>
-    </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J376" s="3"/>
+      <c r="K376" s="3"/>
+    </row>
+    <row r="377" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A377" s="4">
         <v>376</v>
       </c>
@@ -5465,8 +6226,10 @@
       <c r="G377" s="4"/>
       <c r="H377" s="4"/>
       <c r="I377" s="4"/>
-    </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J377" s="4"/>
+      <c r="K377" s="4"/>
+    </row>
+    <row r="378" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A378" s="3">
         <v>377</v>
       </c>
@@ -5478,8 +6241,10 @@
       <c r="G378" s="3"/>
       <c r="H378" s="3"/>
       <c r="I378" s="3"/>
-    </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J378" s="3"/>
+      <c r="K378" s="3"/>
+    </row>
+    <row r="379" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A379" s="4">
         <v>378</v>
       </c>
@@ -5491,8 +6256,10 @@
       <c r="G379" s="4"/>
       <c r="H379" s="4"/>
       <c r="I379" s="4"/>
-    </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J379" s="4"/>
+      <c r="K379" s="4"/>
+    </row>
+    <row r="380" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A380" s="3">
         <v>379</v>
       </c>
@@ -5504,8 +6271,10 @@
       <c r="G380" s="3"/>
       <c r="H380" s="3"/>
       <c r="I380" s="3"/>
-    </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J380" s="3"/>
+      <c r="K380" s="3"/>
+    </row>
+    <row r="381" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A381" s="4">
         <v>380</v>
       </c>
@@ -5517,8 +6286,10 @@
       <c r="G381" s="4"/>
       <c r="H381" s="4"/>
       <c r="I381" s="4"/>
-    </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J381" s="4"/>
+      <c r="K381" s="4"/>
+    </row>
+    <row r="382" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A382" s="3">
         <v>381</v>
       </c>
@@ -5530,8 +6301,10 @@
       <c r="G382" s="3"/>
       <c r="H382" s="3"/>
       <c r="I382" s="3"/>
-    </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J382" s="3"/>
+      <c r="K382" s="3"/>
+    </row>
+    <row r="383" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A383" s="4">
         <v>382</v>
       </c>
@@ -5543,8 +6316,10 @@
       <c r="G383" s="4"/>
       <c r="H383" s="4"/>
       <c r="I383" s="4"/>
-    </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J383" s="4"/>
+      <c r="K383" s="4"/>
+    </row>
+    <row r="384" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A384" s="3">
         <v>383</v>
       </c>
@@ -5556,8 +6331,10 @@
       <c r="G384" s="3"/>
       <c r="H384" s="3"/>
       <c r="I384" s="3"/>
-    </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J384" s="3"/>
+      <c r="K384" s="3"/>
+    </row>
+    <row r="385" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A385" s="4">
         <v>384</v>
       </c>
@@ -5569,8 +6346,10 @@
       <c r="G385" s="4"/>
       <c r="H385" s="4"/>
       <c r="I385" s="4"/>
-    </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J385" s="4"/>
+      <c r="K385" s="4"/>
+    </row>
+    <row r="386" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A386" s="3">
         <v>385</v>
       </c>
@@ -5582,8 +6361,10 @@
       <c r="G386" s="3"/>
       <c r="H386" s="3"/>
       <c r="I386" s="3"/>
-    </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J386" s="3"/>
+      <c r="K386" s="3"/>
+    </row>
+    <row r="387" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A387" s="4">
         <v>386</v>
       </c>
@@ -5595,8 +6376,10 @@
       <c r="G387" s="4"/>
       <c r="H387" s="4"/>
       <c r="I387" s="4"/>
-    </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J387" s="4"/>
+      <c r="K387" s="4"/>
+    </row>
+    <row r="388" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A388" s="3">
         <v>387</v>
       </c>
@@ -5608,8 +6391,10 @@
       <c r="G388" s="3"/>
       <c r="H388" s="3"/>
       <c r="I388" s="3"/>
-    </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J388" s="3"/>
+      <c r="K388" s="3"/>
+    </row>
+    <row r="389" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A389" s="4">
         <v>388</v>
       </c>
@@ -5621,8 +6406,10 @@
       <c r="G389" s="4"/>
       <c r="H389" s="4"/>
       <c r="I389" s="4"/>
-    </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J389" s="4"/>
+      <c r="K389" s="4"/>
+    </row>
+    <row r="390" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A390" s="3">
         <v>389</v>
       </c>
@@ -5634,8 +6421,10 @@
       <c r="G390" s="3"/>
       <c r="H390" s="3"/>
       <c r="I390" s="3"/>
-    </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J390" s="3"/>
+      <c r="K390" s="3"/>
+    </row>
+    <row r="391" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A391" s="4">
         <v>390</v>
       </c>
@@ -5647,8 +6436,10 @@
       <c r="G391" s="4"/>
       <c r="H391" s="4"/>
       <c r="I391" s="4"/>
-    </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J391" s="4"/>
+      <c r="K391" s="4"/>
+    </row>
+    <row r="392" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A392" s="3">
         <v>391</v>
       </c>
@@ -5660,8 +6451,10 @@
       <c r="G392" s="3"/>
       <c r="H392" s="3"/>
       <c r="I392" s="3"/>
-    </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J392" s="3"/>
+      <c r="K392" s="3"/>
+    </row>
+    <row r="393" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A393" s="4">
         <v>392</v>
       </c>
@@ -5673,8 +6466,10 @@
       <c r="G393" s="4"/>
       <c r="H393" s="4"/>
       <c r="I393" s="4"/>
-    </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J393" s="4"/>
+      <c r="K393" s="4"/>
+    </row>
+    <row r="394" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A394" s="3">
         <v>393</v>
       </c>
@@ -5686,8 +6481,10 @@
       <c r="G394" s="3"/>
       <c r="H394" s="3"/>
       <c r="I394" s="3"/>
-    </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J394" s="3"/>
+      <c r="K394" s="3"/>
+    </row>
+    <row r="395" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A395" s="4">
         <v>394</v>
       </c>
@@ -5699,8 +6496,10 @@
       <c r="G395" s="4"/>
       <c r="H395" s="4"/>
       <c r="I395" s="4"/>
-    </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J395" s="4"/>
+      <c r="K395" s="4"/>
+    </row>
+    <row r="396" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A396" s="3">
         <v>395</v>
       </c>
@@ -5712,8 +6511,10 @@
       <c r="G396" s="3"/>
       <c r="H396" s="3"/>
       <c r="I396" s="3"/>
-    </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J396" s="3"/>
+      <c r="K396" s="3"/>
+    </row>
+    <row r="397" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A397" s="4">
         <v>396</v>
       </c>
@@ -5725,8 +6526,10 @@
       <c r="G397" s="4"/>
       <c r="H397" s="4"/>
       <c r="I397" s="4"/>
-    </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J397" s="4"/>
+      <c r="K397" s="4"/>
+    </row>
+    <row r="398" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A398" s="3">
         <v>397</v>
       </c>
@@ -5738,8 +6541,10 @@
       <c r="G398" s="3"/>
       <c r="H398" s="3"/>
       <c r="I398" s="3"/>
-    </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J398" s="3"/>
+      <c r="K398" s="3"/>
+    </row>
+    <row r="399" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A399" s="4">
         <v>398</v>
       </c>
@@ -5751,8 +6556,10 @@
       <c r="G399" s="4"/>
       <c r="H399" s="4"/>
       <c r="I399" s="4"/>
-    </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J399" s="4"/>
+      <c r="K399" s="4"/>
+    </row>
+    <row r="400" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A400" s="3">
         <v>399</v>
       </c>
@@ -5764,8 +6571,10 @@
       <c r="G400" s="3"/>
       <c r="H400" s="3"/>
       <c r="I400" s="3"/>
-    </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J400" s="3"/>
+      <c r="K400" s="3"/>
+    </row>
+    <row r="401" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A401" s="4">
         <v>400</v>
       </c>
@@ -5777,8 +6586,10 @@
       <c r="G401" s="4"/>
       <c r="H401" s="4"/>
       <c r="I401" s="4"/>
-    </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J401" s="4"/>
+      <c r="K401" s="4"/>
+    </row>
+    <row r="402" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A402" s="3">
         <v>401</v>
       </c>
@@ -5790,8 +6601,10 @@
       <c r="G402" s="3"/>
       <c r="H402" s="3"/>
       <c r="I402" s="3"/>
-    </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J402" s="3"/>
+      <c r="K402" s="3"/>
+    </row>
+    <row r="403" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A403" s="4">
         <v>402</v>
       </c>
@@ -5803,8 +6616,10 @@
       <c r="G403" s="4"/>
       <c r="H403" s="4"/>
       <c r="I403" s="4"/>
-    </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J403" s="4"/>
+      <c r="K403" s="4"/>
+    </row>
+    <row r="404" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A404" s="3">
         <v>403</v>
       </c>
@@ -5816,8 +6631,10 @@
       <c r="G404" s="3"/>
       <c r="H404" s="3"/>
       <c r="I404" s="3"/>
-    </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J404" s="3"/>
+      <c r="K404" s="3"/>
+    </row>
+    <row r="405" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A405" s="4">
         <v>404</v>
       </c>
@@ -5829,8 +6646,10 @@
       <c r="G405" s="4"/>
       <c r="H405" s="4"/>
       <c r="I405" s="4"/>
-    </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J405" s="4"/>
+      <c r="K405" s="4"/>
+    </row>
+    <row r="406" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A406" s="3">
         <v>405</v>
       </c>
@@ -5842,8 +6661,10 @@
       <c r="G406" s="3"/>
       <c r="H406" s="3"/>
       <c r="I406" s="3"/>
-    </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J406" s="3"/>
+      <c r="K406" s="3"/>
+    </row>
+    <row r="407" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A407" s="4">
         <v>406</v>
       </c>
@@ -5855,8 +6676,10 @@
       <c r="G407" s="4"/>
       <c r="H407" s="4"/>
       <c r="I407" s="4"/>
-    </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J407" s="4"/>
+      <c r="K407" s="4"/>
+    </row>
+    <row r="408" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A408" s="3">
         <v>407</v>
       </c>
@@ -5868,8 +6691,10 @@
       <c r="G408" s="3"/>
       <c r="H408" s="3"/>
       <c r="I408" s="3"/>
-    </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J408" s="3"/>
+      <c r="K408" s="3"/>
+    </row>
+    <row r="409" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A409" s="4">
         <v>408</v>
       </c>
@@ -5881,8 +6706,10 @@
       <c r="G409" s="4"/>
       <c r="H409" s="4"/>
       <c r="I409" s="4"/>
-    </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J409" s="4"/>
+      <c r="K409" s="4"/>
+    </row>
+    <row r="410" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A410" s="3">
         <v>409</v>
       </c>
@@ -5894,8 +6721,10 @@
       <c r="G410" s="3"/>
       <c r="H410" s="3"/>
       <c r="I410" s="3"/>
-    </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J410" s="3"/>
+      <c r="K410" s="3"/>
+    </row>
+    <row r="411" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A411" s="4">
         <v>410</v>
       </c>
@@ -5907,8 +6736,10 @@
       <c r="G411" s="4"/>
       <c r="H411" s="4"/>
       <c r="I411" s="4"/>
-    </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J411" s="4"/>
+      <c r="K411" s="4"/>
+    </row>
+    <row r="412" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A412" s="3">
         <v>411</v>
       </c>
@@ -5920,8 +6751,10 @@
       <c r="G412" s="3"/>
       <c r="H412" s="3"/>
       <c r="I412" s="3"/>
-    </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J412" s="3"/>
+      <c r="K412" s="3"/>
+    </row>
+    <row r="413" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A413" s="4">
         <v>412</v>
       </c>
@@ -5933,8 +6766,10 @@
       <c r="G413" s="4"/>
       <c r="H413" s="4"/>
       <c r="I413" s="4"/>
-    </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J413" s="4"/>
+      <c r="K413" s="4"/>
+    </row>
+    <row r="414" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A414" s="3">
         <v>413</v>
       </c>
@@ -5946,8 +6781,10 @@
       <c r="G414" s="3"/>
       <c r="H414" s="3"/>
       <c r="I414" s="3"/>
-    </row>
-    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J414" s="3"/>
+      <c r="K414" s="3"/>
+    </row>
+    <row r="415" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A415" s="4">
         <v>414</v>
       </c>
@@ -5959,8 +6796,10 @@
       <c r="G415" s="4"/>
       <c r="H415" s="4"/>
       <c r="I415" s="4"/>
-    </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J415" s="4"/>
+      <c r="K415" s="4"/>
+    </row>
+    <row r="416" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A416" s="3">
         <v>415</v>
       </c>
@@ -5972,8 +6811,10 @@
       <c r="G416" s="3"/>
       <c r="H416" s="3"/>
       <c r="I416" s="3"/>
-    </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J416" s="3"/>
+      <c r="K416" s="3"/>
+    </row>
+    <row r="417" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A417" s="4">
         <v>416</v>
       </c>
@@ -5985,8 +6826,10 @@
       <c r="G417" s="4"/>
       <c r="H417" s="4"/>
       <c r="I417" s="4"/>
-    </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J417" s="4"/>
+      <c r="K417" s="4"/>
+    </row>
+    <row r="418" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A418" s="3">
         <v>417</v>
       </c>
@@ -5998,8 +6841,10 @@
       <c r="G418" s="3"/>
       <c r="H418" s="3"/>
       <c r="I418" s="3"/>
-    </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J418" s="3"/>
+      <c r="K418" s="3"/>
+    </row>
+    <row r="419" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A419" s="4">
         <v>418</v>
       </c>
@@ -6011,8 +6856,10 @@
       <c r="G419" s="4"/>
       <c r="H419" s="4"/>
       <c r="I419" s="4"/>
-    </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J419" s="4"/>
+      <c r="K419" s="4"/>
+    </row>
+    <row r="420" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A420" s="3">
         <v>419</v>
       </c>
@@ -6024,8 +6871,10 @@
       <c r="G420" s="3"/>
       <c r="H420" s="3"/>
       <c r="I420" s="3"/>
-    </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J420" s="3"/>
+      <c r="K420" s="3"/>
+    </row>
+    <row r="421" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A421" s="4">
         <v>420</v>
       </c>
@@ -6037,8 +6886,10 @@
       <c r="G421" s="4"/>
       <c r="H421" s="4"/>
       <c r="I421" s="4"/>
-    </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J421" s="4"/>
+      <c r="K421" s="4"/>
+    </row>
+    <row r="422" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A422" s="3">
         <v>421</v>
       </c>
@@ -6050,8 +6901,10 @@
       <c r="G422" s="3"/>
       <c r="H422" s="3"/>
       <c r="I422" s="3"/>
-    </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J422" s="3"/>
+      <c r="K422" s="3"/>
+    </row>
+    <row r="423" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A423" s="4">
         <v>422</v>
       </c>
@@ -6063,8 +6916,10 @@
       <c r="G423" s="4"/>
       <c r="H423" s="4"/>
       <c r="I423" s="4"/>
-    </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J423" s="4"/>
+      <c r="K423" s="4"/>
+    </row>
+    <row r="424" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A424" s="3">
         <v>423</v>
       </c>
@@ -6076,8 +6931,10 @@
       <c r="G424" s="3"/>
       <c r="H424" s="3"/>
       <c r="I424" s="3"/>
-    </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J424" s="3"/>
+      <c r="K424" s="3"/>
+    </row>
+    <row r="425" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A425" s="4">
         <v>424</v>
       </c>
@@ -6089,8 +6946,10 @@
       <c r="G425" s="4"/>
       <c r="H425" s="4"/>
       <c r="I425" s="4"/>
-    </row>
-    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J425" s="4"/>
+      <c r="K425" s="4"/>
+    </row>
+    <row r="426" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A426" s="3">
         <v>425</v>
       </c>
@@ -6102,8 +6961,10 @@
       <c r="G426" s="3"/>
       <c r="H426" s="3"/>
       <c r="I426" s="3"/>
-    </row>
-    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J426" s="3"/>
+      <c r="K426" s="3"/>
+    </row>
+    <row r="427" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A427" s="4">
         <v>426</v>
       </c>
@@ -6115,8 +6976,10 @@
       <c r="G427" s="4"/>
       <c r="H427" s="4"/>
       <c r="I427" s="4"/>
-    </row>
-    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J427" s="4"/>
+      <c r="K427" s="4"/>
+    </row>
+    <row r="428" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A428" s="3">
         <v>427</v>
       </c>
@@ -6128,8 +6991,10 @@
       <c r="G428" s="3"/>
       <c r="H428" s="3"/>
       <c r="I428" s="3"/>
-    </row>
-    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J428" s="3"/>
+      <c r="K428" s="3"/>
+    </row>
+    <row r="429" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A429" s="4">
         <v>428</v>
       </c>
@@ -6141,8 +7006,10 @@
       <c r="G429" s="4"/>
       <c r="H429" s="4"/>
       <c r="I429" s="4"/>
-    </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J429" s="4"/>
+      <c r="K429" s="4"/>
+    </row>
+    <row r="430" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A430" s="3">
         <v>429</v>
       </c>
@@ -6154,8 +7021,10 @@
       <c r="G430" s="3"/>
       <c r="H430" s="3"/>
       <c r="I430" s="3"/>
-    </row>
-    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J430" s="3"/>
+      <c r="K430" s="3"/>
+    </row>
+    <row r="431" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A431" s="4">
         <v>430</v>
       </c>
@@ -6167,8 +7036,10 @@
       <c r="G431" s="4"/>
       <c r="H431" s="4"/>
       <c r="I431" s="4"/>
-    </row>
-    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J431" s="4"/>
+      <c r="K431" s="4"/>
+    </row>
+    <row r="432" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A432" s="3">
         <v>431</v>
       </c>
@@ -6180,8 +7051,10 @@
       <c r="G432" s="3"/>
       <c r="H432" s="3"/>
       <c r="I432" s="3"/>
-    </row>
-    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J432" s="3"/>
+      <c r="K432" s="3"/>
+    </row>
+    <row r="433" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A433" s="4">
         <v>432</v>
       </c>
@@ -6193,8 +7066,10 @@
       <c r="G433" s="4"/>
       <c r="H433" s="4"/>
       <c r="I433" s="4"/>
-    </row>
-    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J433" s="4"/>
+      <c r="K433" s="4"/>
+    </row>
+    <row r="434" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A434" s="3">
         <v>433</v>
       </c>
@@ -6206,8 +7081,10 @@
       <c r="G434" s="3"/>
       <c r="H434" s="3"/>
       <c r="I434" s="3"/>
-    </row>
-    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J434" s="3"/>
+      <c r="K434" s="3"/>
+    </row>
+    <row r="435" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A435" s="4">
         <v>434</v>
       </c>
@@ -6219,8 +7096,10 @@
       <c r="G435" s="4"/>
       <c r="H435" s="4"/>
       <c r="I435" s="4"/>
-    </row>
-    <row r="436" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J435" s="4"/>
+      <c r="K435" s="4"/>
+    </row>
+    <row r="436" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A436" s="3">
         <v>435</v>
       </c>
@@ -6232,8 +7111,10 @@
       <c r="G436" s="3"/>
       <c r="H436" s="3"/>
       <c r="I436" s="3"/>
-    </row>
-    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J436" s="3"/>
+      <c r="K436" s="3"/>
+    </row>
+    <row r="437" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A437" s="4">
         <v>436</v>
       </c>
@@ -6245,8 +7126,10 @@
       <c r="G437" s="4"/>
       <c r="H437" s="4"/>
       <c r="I437" s="4"/>
-    </row>
-    <row r="438" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J437" s="4"/>
+      <c r="K437" s="4"/>
+    </row>
+    <row r="438" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A438" s="3">
         <v>437</v>
       </c>
@@ -6258,8 +7141,10 @@
       <c r="G438" s="3"/>
       <c r="H438" s="3"/>
       <c r="I438" s="3"/>
-    </row>
-    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J438" s="3"/>
+      <c r="K438" s="3"/>
+    </row>
+    <row r="439" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A439" s="4">
         <v>438</v>
       </c>
@@ -6271,8 +7156,10 @@
       <c r="G439" s="4"/>
       <c r="H439" s="4"/>
       <c r="I439" s="4"/>
-    </row>
-    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J439" s="4"/>
+      <c r="K439" s="4"/>
+    </row>
+    <row r="440" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A440" s="3">
         <v>439</v>
       </c>
@@ -6284,8 +7171,10 @@
       <c r="G440" s="3"/>
       <c r="H440" s="3"/>
       <c r="I440" s="3"/>
-    </row>
-    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J440" s="3"/>
+      <c r="K440" s="3"/>
+    </row>
+    <row r="441" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A441" s="4">
         <v>440</v>
       </c>
@@ -6297,8 +7186,10 @@
       <c r="G441" s="4"/>
       <c r="H441" s="4"/>
       <c r="I441" s="4"/>
-    </row>
-    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J441" s="4"/>
+      <c r="K441" s="4"/>
+    </row>
+    <row r="442" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A442" s="3">
         <v>441</v>
       </c>
@@ -6310,8 +7201,10 @@
       <c r="G442" s="3"/>
       <c r="H442" s="3"/>
       <c r="I442" s="3"/>
-    </row>
-    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J442" s="3"/>
+      <c r="K442" s="3"/>
+    </row>
+    <row r="443" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A443" s="4">
         <v>442</v>
       </c>
@@ -6323,8 +7216,10 @@
       <c r="G443" s="4"/>
       <c r="H443" s="4"/>
       <c r="I443" s="4"/>
-    </row>
-    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J443" s="4"/>
+      <c r="K443" s="4"/>
+    </row>
+    <row r="444" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A444" s="3">
         <v>443</v>
       </c>
@@ -6336,8 +7231,10 @@
       <c r="G444" s="3"/>
       <c r="H444" s="3"/>
       <c r="I444" s="3"/>
-    </row>
-    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J444" s="3"/>
+      <c r="K444" s="3"/>
+    </row>
+    <row r="445" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A445" s="4">
         <v>444</v>
       </c>
@@ -6349,8 +7246,10 @@
       <c r="G445" s="4"/>
       <c r="H445" s="4"/>
       <c r="I445" s="4"/>
-    </row>
-    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J445" s="4"/>
+      <c r="K445" s="4"/>
+    </row>
+    <row r="446" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A446" s="3">
         <v>445</v>
       </c>
@@ -6362,8 +7261,10 @@
       <c r="G446" s="3"/>
       <c r="H446" s="3"/>
       <c r="I446" s="3"/>
-    </row>
-    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J446" s="3"/>
+      <c r="K446" s="3"/>
+    </row>
+    <row r="447" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A447" s="4">
         <v>446</v>
       </c>
@@ -6375,8 +7276,10 @@
       <c r="G447" s="4"/>
       <c r="H447" s="4"/>
       <c r="I447" s="4"/>
-    </row>
-    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J447" s="4"/>
+      <c r="K447" s="4"/>
+    </row>
+    <row r="448" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A448" s="3">
         <v>447</v>
       </c>
@@ -6388,8 +7291,10 @@
       <c r="G448" s="3"/>
       <c r="H448" s="3"/>
       <c r="I448" s="3"/>
-    </row>
-    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J448" s="3"/>
+      <c r="K448" s="3"/>
+    </row>
+    <row r="449" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A449" s="4">
         <v>448</v>
       </c>
@@ -6401,8 +7306,10 @@
       <c r="G449" s="4"/>
       <c r="H449" s="4"/>
       <c r="I449" s="4"/>
-    </row>
-    <row r="450" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J449" s="4"/>
+      <c r="K449" s="4"/>
+    </row>
+    <row r="450" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A450" s="3">
         <v>449</v>
       </c>
@@ -6414,8 +7321,10 @@
       <c r="G450" s="3"/>
       <c r="H450" s="3"/>
       <c r="I450" s="3"/>
-    </row>
-    <row r="451" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J450" s="3"/>
+      <c r="K450" s="3"/>
+    </row>
+    <row r="451" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A451" s="4">
         <v>450</v>
       </c>
@@ -6427,8 +7336,10 @@
       <c r="G451" s="4"/>
       <c r="H451" s="4"/>
       <c r="I451" s="4"/>
-    </row>
-    <row r="452" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J451" s="4"/>
+      <c r="K451" s="4"/>
+    </row>
+    <row r="452" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A452" s="3">
         <v>451</v>
       </c>
@@ -6440,8 +7351,10 @@
       <c r="G452" s="3"/>
       <c r="H452" s="3"/>
       <c r="I452" s="3"/>
-    </row>
-    <row r="453" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J452" s="3"/>
+      <c r="K452" s="3"/>
+    </row>
+    <row r="453" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A453" s="4">
         <v>452</v>
       </c>
@@ -6453,8 +7366,10 @@
       <c r="G453" s="4"/>
       <c r="H453" s="4"/>
       <c r="I453" s="4"/>
-    </row>
-    <row r="454" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J453" s="4"/>
+      <c r="K453" s="4"/>
+    </row>
+    <row r="454" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A454" s="3">
         <v>453</v>
       </c>
@@ -6466,8 +7381,10 @@
       <c r="G454" s="3"/>
       <c r="H454" s="3"/>
       <c r="I454" s="3"/>
-    </row>
-    <row r="455" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J454" s="3"/>
+      <c r="K454" s="3"/>
+    </row>
+    <row r="455" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A455" s="4">
         <v>454</v>
       </c>
@@ -6479,8 +7396,10 @@
       <c r="G455" s="4"/>
       <c r="H455" s="4"/>
       <c r="I455" s="4"/>
-    </row>
-    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J455" s="4"/>
+      <c r="K455" s="4"/>
+    </row>
+    <row r="456" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A456" s="3">
         <v>455</v>
       </c>
@@ -6492,8 +7411,10 @@
       <c r="G456" s="3"/>
       <c r="H456" s="3"/>
       <c r="I456" s="3"/>
-    </row>
-    <row r="457" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J456" s="3"/>
+      <c r="K456" s="3"/>
+    </row>
+    <row r="457" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A457" s="4">
         <v>456</v>
       </c>
@@ -6505,8 +7426,10 @@
       <c r="G457" s="4"/>
       <c r="H457" s="4"/>
       <c r="I457" s="4"/>
-    </row>
-    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J457" s="4"/>
+      <c r="K457" s="4"/>
+    </row>
+    <row r="458" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A458" s="3">
         <v>457</v>
       </c>
@@ -6518,8 +7441,10 @@
       <c r="G458" s="3"/>
       <c r="H458" s="3"/>
       <c r="I458" s="3"/>
-    </row>
-    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J458" s="3"/>
+      <c r="K458" s="3"/>
+    </row>
+    <row r="459" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A459" s="4">
         <v>458</v>
       </c>
@@ -6531,8 +7456,10 @@
       <c r="G459" s="4"/>
       <c r="H459" s="4"/>
       <c r="I459" s="4"/>
-    </row>
-    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J459" s="4"/>
+      <c r="K459" s="4"/>
+    </row>
+    <row r="460" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A460" s="3">
         <v>459</v>
       </c>
@@ -6544,8 +7471,10 @@
       <c r="G460" s="3"/>
       <c r="H460" s="3"/>
       <c r="I460" s="3"/>
-    </row>
-    <row r="461" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J460" s="3"/>
+      <c r="K460" s="3"/>
+    </row>
+    <row r="461" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A461" s="4">
         <v>460</v>
       </c>
@@ -6557,8 +7486,10 @@
       <c r="G461" s="4"/>
       <c r="H461" s="4"/>
       <c r="I461" s="4"/>
-    </row>
-    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J461" s="4"/>
+      <c r="K461" s="4"/>
+    </row>
+    <row r="462" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A462" s="3">
         <v>461</v>
       </c>
@@ -6570,8 +7501,10 @@
       <c r="G462" s="3"/>
       <c r="H462" s="3"/>
       <c r="I462" s="3"/>
-    </row>
-    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J462" s="3"/>
+      <c r="K462" s="3"/>
+    </row>
+    <row r="463" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A463" s="4">
         <v>462</v>
       </c>
@@ -6583,8 +7516,10 @@
       <c r="G463" s="4"/>
       <c r="H463" s="4"/>
       <c r="I463" s="4"/>
-    </row>
-    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J463" s="4"/>
+      <c r="K463" s="4"/>
+    </row>
+    <row r="464" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A464" s="3">
         <v>463</v>
       </c>
@@ -6596,8 +7531,10 @@
       <c r="G464" s="3"/>
       <c r="H464" s="3"/>
       <c r="I464" s="3"/>
-    </row>
-    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J464" s="3"/>
+      <c r="K464" s="3"/>
+    </row>
+    <row r="465" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A465" s="4">
         <v>464</v>
       </c>
@@ -6609,8 +7546,10 @@
       <c r="G465" s="4"/>
       <c r="H465" s="4"/>
       <c r="I465" s="4"/>
-    </row>
-    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J465" s="4"/>
+      <c r="K465" s="4"/>
+    </row>
+    <row r="466" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A466" s="3">
         <v>465</v>
       </c>
@@ -6622,8 +7561,10 @@
       <c r="G466" s="3"/>
       <c r="H466" s="3"/>
       <c r="I466" s="3"/>
-    </row>
-    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J466" s="3"/>
+      <c r="K466" s="3"/>
+    </row>
+    <row r="467" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A467" s="4">
         <v>466</v>
       </c>
@@ -6635,8 +7576,10 @@
       <c r="G467" s="4"/>
       <c r="H467" s="4"/>
       <c r="I467" s="4"/>
-    </row>
-    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J467" s="4"/>
+      <c r="K467" s="4"/>
+    </row>
+    <row r="468" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A468" s="3">
         <v>467</v>
       </c>
@@ -6648,8 +7591,10 @@
       <c r="G468" s="3"/>
       <c r="H468" s="3"/>
       <c r="I468" s="3"/>
-    </row>
-    <row r="469" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J468" s="3"/>
+      <c r="K468" s="3"/>
+    </row>
+    <row r="469" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A469" s="4">
         <v>468</v>
       </c>
@@ -6661,8 +7606,10 @@
       <c r="G469" s="4"/>
       <c r="H469" s="4"/>
       <c r="I469" s="4"/>
-    </row>
-    <row r="470" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J469" s="4"/>
+      <c r="K469" s="4"/>
+    </row>
+    <row r="470" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A470" s="3">
         <v>469</v>
       </c>
@@ -6674,8 +7621,10 @@
       <c r="G470" s="3"/>
       <c r="H470" s="3"/>
       <c r="I470" s="3"/>
-    </row>
-    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J470" s="3"/>
+      <c r="K470" s="3"/>
+    </row>
+    <row r="471" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A471" s="4">
         <v>470</v>
       </c>
@@ -6687,8 +7636,10 @@
       <c r="G471" s="4"/>
       <c r="H471" s="4"/>
       <c r="I471" s="4"/>
-    </row>
-    <row r="472" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J471" s="4"/>
+      <c r="K471" s="4"/>
+    </row>
+    <row r="472" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A472" s="3">
         <v>471</v>
       </c>
@@ -6700,8 +7651,10 @@
       <c r="G472" s="3"/>
       <c r="H472" s="3"/>
       <c r="I472" s="3"/>
-    </row>
-    <row r="473" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J472" s="3"/>
+      <c r="K472" s="3"/>
+    </row>
+    <row r="473" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A473" s="4">
         <v>472</v>
       </c>
@@ -6713,8 +7666,10 @@
       <c r="G473" s="4"/>
       <c r="H473" s="4"/>
       <c r="I473" s="4"/>
-    </row>
-    <row r="474" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J473" s="4"/>
+      <c r="K473" s="4"/>
+    </row>
+    <row r="474" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A474" s="3">
         <v>473</v>
       </c>
@@ -6726,8 +7681,10 @@
       <c r="G474" s="3"/>
       <c r="H474" s="3"/>
       <c r="I474" s="3"/>
-    </row>
-    <row r="475" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J474" s="3"/>
+      <c r="K474" s="3"/>
+    </row>
+    <row r="475" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A475" s="4">
         <v>474</v>
       </c>
@@ -6739,8 +7696,10 @@
       <c r="G475" s="4"/>
       <c r="H475" s="4"/>
       <c r="I475" s="4"/>
-    </row>
-    <row r="476" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J475" s="4"/>
+      <c r="K475" s="4"/>
+    </row>
+    <row r="476" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A476" s="3">
         <v>475</v>
       </c>
@@ -6752,8 +7711,10 @@
       <c r="G476" s="3"/>
       <c r="H476" s="3"/>
       <c r="I476" s="3"/>
-    </row>
-    <row r="477" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J476" s="3"/>
+      <c r="K476" s="3"/>
+    </row>
+    <row r="477" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A477" s="4">
         <v>476</v>
       </c>
@@ -6765,8 +7726,10 @@
       <c r="G477" s="4"/>
       <c r="H477" s="4"/>
       <c r="I477" s="4"/>
-    </row>
-    <row r="478" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J477" s="4"/>
+      <c r="K477" s="4"/>
+    </row>
+    <row r="478" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A478" s="3">
         <v>477</v>
       </c>
@@ -6778,8 +7741,10 @@
       <c r="G478" s="3"/>
       <c r="H478" s="3"/>
       <c r="I478" s="3"/>
-    </row>
-    <row r="479" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J478" s="3"/>
+      <c r="K478" s="3"/>
+    </row>
+    <row r="479" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A479" s="4">
         <v>478</v>
       </c>
@@ -6791,8 +7756,10 @@
       <c r="G479" s="4"/>
       <c r="H479" s="4"/>
       <c r="I479" s="4"/>
-    </row>
-    <row r="480" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J479" s="4"/>
+      <c r="K479" s="4"/>
+    </row>
+    <row r="480" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A480" s="3">
         <v>479</v>
       </c>
@@ -6804,8 +7771,10 @@
       <c r="G480" s="3"/>
       <c r="H480" s="3"/>
       <c r="I480" s="3"/>
-    </row>
-    <row r="481" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J480" s="3"/>
+      <c r="K480" s="3"/>
+    </row>
+    <row r="481" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A481" s="4">
         <v>480</v>
       </c>
@@ -6817,8 +7786,10 @@
       <c r="G481" s="4"/>
       <c r="H481" s="4"/>
       <c r="I481" s="4"/>
-    </row>
-    <row r="482" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J481" s="4"/>
+      <c r="K481" s="4"/>
+    </row>
+    <row r="482" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A482" s="3">
         <v>481</v>
       </c>
@@ -6830,8 +7801,10 @@
       <c r="G482" s="3"/>
       <c r="H482" s="3"/>
       <c r="I482" s="3"/>
-    </row>
-    <row r="483" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J482" s="3"/>
+      <c r="K482" s="3"/>
+    </row>
+    <row r="483" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A483" s="4">
         <v>482</v>
       </c>
@@ -6843,8 +7816,10 @@
       <c r="G483" s="4"/>
       <c r="H483" s="4"/>
       <c r="I483" s="4"/>
-    </row>
-    <row r="484" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J483" s="4"/>
+      <c r="K483" s="4"/>
+    </row>
+    <row r="484" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A484" s="3">
         <v>483</v>
       </c>
@@ -6856,8 +7831,10 @@
       <c r="G484" s="3"/>
       <c r="H484" s="3"/>
       <c r="I484" s="3"/>
-    </row>
-    <row r="485" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J484" s="3"/>
+      <c r="K484" s="3"/>
+    </row>
+    <row r="485" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A485" s="4">
         <v>484</v>
       </c>
@@ -6869,8 +7846,10 @@
       <c r="G485" s="4"/>
       <c r="H485" s="4"/>
       <c r="I485" s="4"/>
-    </row>
-    <row r="486" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J485" s="4"/>
+      <c r="K485" s="4"/>
+    </row>
+    <row r="486" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A486" s="3">
         <v>485</v>
       </c>
@@ -6882,8 +7861,10 @@
       <c r="G486" s="3"/>
       <c r="H486" s="3"/>
       <c r="I486" s="3"/>
-    </row>
-    <row r="487" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J486" s="3"/>
+      <c r="K486" s="3"/>
+    </row>
+    <row r="487" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A487" s="4">
         <v>486</v>
       </c>
@@ -6895,8 +7876,10 @@
       <c r="G487" s="4"/>
       <c r="H487" s="4"/>
       <c r="I487" s="4"/>
-    </row>
-    <row r="488" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J487" s="4"/>
+      <c r="K487" s="4"/>
+    </row>
+    <row r="488" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A488" s="3">
         <v>487</v>
       </c>
@@ -6908,8 +7891,10 @@
       <c r="G488" s="3"/>
       <c r="H488" s="3"/>
       <c r="I488" s="3"/>
-    </row>
-    <row r="489" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J488" s="3"/>
+      <c r="K488" s="3"/>
+    </row>
+    <row r="489" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A489" s="4">
         <v>488</v>
       </c>
@@ -6921,8 +7906,10 @@
       <c r="G489" s="4"/>
       <c r="H489" s="4"/>
       <c r="I489" s="4"/>
-    </row>
-    <row r="490" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J489" s="4"/>
+      <c r="K489" s="4"/>
+    </row>
+    <row r="490" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A490" s="3">
         <v>489</v>
       </c>
@@ -6934,8 +7921,10 @@
       <c r="G490" s="3"/>
       <c r="H490" s="3"/>
       <c r="I490" s="3"/>
-    </row>
-    <row r="491" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J490" s="3"/>
+      <c r="K490" s="3"/>
+    </row>
+    <row r="491" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A491" s="4">
         <v>490</v>
       </c>
@@ -6947,8 +7936,10 @@
       <c r="G491" s="4"/>
       <c r="H491" s="4"/>
       <c r="I491" s="4"/>
-    </row>
-    <row r="492" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J491" s="4"/>
+      <c r="K491" s="4"/>
+    </row>
+    <row r="492" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A492" s="3">
         <v>491</v>
       </c>
@@ -6960,8 +7951,10 @@
       <c r="G492" s="3"/>
       <c r="H492" s="3"/>
       <c r="I492" s="3"/>
-    </row>
-    <row r="493" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J492" s="3"/>
+      <c r="K492" s="3"/>
+    </row>
+    <row r="493" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A493" s="4">
         <v>492</v>
       </c>
@@ -6973,8 +7966,10 @@
       <c r="G493" s="4"/>
       <c r="H493" s="4"/>
       <c r="I493" s="4"/>
-    </row>
-    <row r="494" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J493" s="4"/>
+      <c r="K493" s="4"/>
+    </row>
+    <row r="494" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A494" s="3">
         <v>493</v>
       </c>
@@ -6986,8 +7981,10 @@
       <c r="G494" s="3"/>
       <c r="H494" s="3"/>
       <c r="I494" s="3"/>
-    </row>
-    <row r="495" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J494" s="3"/>
+      <c r="K494" s="3"/>
+    </row>
+    <row r="495" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A495" s="4">
         <v>494</v>
       </c>
@@ -6999,8 +7996,10 @@
       <c r="G495" s="4"/>
       <c r="H495" s="4"/>
       <c r="I495" s="4"/>
-    </row>
-    <row r="496" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J495" s="4"/>
+      <c r="K495" s="4"/>
+    </row>
+    <row r="496" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A496" s="3">
         <v>495</v>
       </c>
@@ -7012,8 +8011,10 @@
       <c r="G496" s="3"/>
       <c r="H496" s="3"/>
       <c r="I496" s="3"/>
-    </row>
-    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J496" s="3"/>
+      <c r="K496" s="3"/>
+    </row>
+    <row r="497" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A497" s="4">
         <v>496</v>
       </c>
@@ -7025,8 +8026,10 @@
       <c r="G497" s="4"/>
       <c r="H497" s="4"/>
       <c r="I497" s="4"/>
-    </row>
-    <row r="498" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J497" s="4"/>
+      <c r="K497" s="4"/>
+    </row>
+    <row r="498" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A498" s="3">
         <v>497</v>
       </c>
@@ -7038,8 +8041,10 @@
       <c r="G498" s="3"/>
       <c r="H498" s="3"/>
       <c r="I498" s="3"/>
-    </row>
-    <row r="499" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J498" s="3"/>
+      <c r="K498" s="3"/>
+    </row>
+    <row r="499" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A499" s="4">
         <v>498</v>
       </c>
@@ -7051,8 +8056,10 @@
       <c r="G499" s="4"/>
       <c r="H499" s="4"/>
       <c r="I499" s="4"/>
-    </row>
-    <row r="500" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J499" s="4"/>
+      <c r="K499" s="4"/>
+    </row>
+    <row r="500" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A500" s="3">
         <v>499</v>
       </c>
@@ -7064,8 +8071,10 @@
       <c r="G500" s="3"/>
       <c r="H500" s="3"/>
       <c r="I500" s="3"/>
-    </row>
-    <row r="501" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J500" s="3"/>
+      <c r="K500" s="3"/>
+    </row>
+    <row r="501" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A501" s="4">
         <v>500</v>
       </c>
@@ -7077,9 +8086,11 @@
       <c r="G501" s="4"/>
       <c r="H501" s="4"/>
       <c r="I501" s="4"/>
+      <c r="J501" s="4"/>
+      <c r="K501" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I501"/>
+  <autoFilter ref="A1:K501"/>
   <dataValidations count="6">
     <dataValidation type="list" showErrorMessage="1" errorTitle="Bộ phận không hợp lệ" error="Chọn một bộ phận trong danh sách." sqref="B10:B501">
       <formula1>"QA,XSX,CĐ,Kho,QC,RD"</formula1>
@@ -7093,10 +8104,10 @@
     <dataValidation type="list" showErrorMessage="1" errorTitle="Phân loại không hợp lệ" error="Chọn một trong năm phân loại quyền chuẩn." sqref="E2:E501">
       <formula1>"Chỉ xem,QA – Cập nhật 4 mốc hoàn thành,Quản lý QA,Bộ phận quản lý thiết bị – Xếp lịch thẩm định,Quản lý bộ phận quản lý thiết bị"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I10:I501">
+    <dataValidation type="list" allowBlank="1" sqref="K10:K501">
       <formula1>"Có,Không"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I501">
+    <dataValidation type="list" allowBlank="1" sqref="K2:K501">
       <formula1>"Có,Không"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7115,82 +8126,82 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:1" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/public/templates/phan-quyen-vmp.xlsx
+++ b/public/templates/phan-quyen-vmp.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>STT</t>
   </si>
@@ -56,13 +56,16 @@
     <t>Mã nhân viên hiện không bắt buộc; có thể để trống và bổ sung sau. Hệ thống tạm khớp bằng Họ và tên có dấu, không phân biệt hoa thường và khoảng trắng.</t>
   </si>
   <si>
-    <t>Bốn cột phạm vi nhập mã danh mục chuẩn, nhiều giá trị cách nhau bằng dấu chấm phẩy. Mỗi xưởng phải thuộc một bộ phận đã chọn, mỗi khu vực thuộc một xưởng đã chọn và mỗi line thuộc một khu vực đã chọn.</t>
+    <t>Nhân sự QA để trống bốn cột phạm vi; quyền QA phát sinh từ phân công từng hạng mục.</t>
   </si>
   <si>
-    <t>Muốn cấp toàn bộ ở một tầng, nhập mã lựa chọn Toàn bộ đã được cấu hình trong danh mục; ô trống không có nghĩa là toàn bộ.</t>
+    <t>Các phân loại ngoài QA vẫn phải nhập đủ bộ phận, xưởng, khu vực và line.</t>
   </si>
   <si>
-    <t>Email nhận tài khoản: nếu trùng email của tài khoản hệ thống, danh bạ tự nối đúng user_id. Không dùng chung một email cho hai người.</t>
+    <t>Với phân loại ngoài QA, bốn cột phạm vi nhập mã danh mục chuẩn, nhiều giá trị cách nhau bằng dấu chấm phẩy. Mỗi xưởng phải thuộc một bộ phận đã chọn, mỗi khu vực thuộc một xưởng đã chọn và mỗi line thuộc một khu vực đã chọn.</t>
+  </si>
+  <si>
+    <t>Email chỉ dùng nhận diện ứng viên; Admin phải nối tài khoản trên web trước khi quyền có hiệu lực.</t>
   </si>
   <si>
     <t>Xác nhận gửi email: chọn Có sau khi đã gửi thông tin tài khoản; không có chức năng tự động gửi email trong file này.</t>
@@ -8118,7 +8121,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -8204,6 +8207,11 @@
         <v>26</v>
       </c>
     </row>
+    <row r="17" ht="30" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
